--- a/kitchenaid/Kitchenaid Service Playbook - Export.xlsx
+++ b/kitchenaid/Kitchenaid Service Playbook - Export.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerom\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://groupefnac-my.sharepoint.com/personal/jerome_leconte_fnacdarty_com/Documents/Documents/Claude/Projects/HUB Drive constructeurs/kitchenaid/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8EB6A6B9-2893-4016-B633-D46B9B01F78D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D191DE27-C82E-4060-B018-A3726B0C0434}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="41496" windowHeight="16776" xr2:uid="{319933B0-C742-484C-B204-6CB521CC8E9B}"/>
+    <workbookView xWindow="-28440" yWindow="1764" windowWidth="30960" windowHeight="12012" xr2:uid="{AD2C4DC7-910B-4E7E-9626-5CE3A7B63C44}"/>
   </bookViews>
   <sheets>
     <sheet name="query (10)" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="query__10" localSheetId="0" hidden="1">'query (10)'!$A$1:$F$261</definedName>
+    <definedName name="query__10" localSheetId="0" hidden="1">'query (10)'!$A$1:$F$271</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
@@ -24,14 +24,14 @@
 
 <file path=xl/connections.xml><?xml version="1.0" encoding="utf-8"?>
 <connections xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16">
-  <connection id="1" xr16:uid="{B9C41BFD-FD2A-4D1C-9E77-F556B6AD3AE7}" odcFile="C:\Users\jerom\Downloads\query (10).iqy" keepAlive="1" name="query (10)" type="5" refreshedVersion="8" minRefreshableVersion="3" saveData="1">
+  <connection id="1" xr16:uid="{ADF555CE-978C-4982-9EE9-CEEC1A45DD5B}" odcFile="C:\Users\jerom\OneDrive - FNAC\Documents\Claude\Projects\HUB Drive constructeurs\kitchenaid\query (10).iqy" keepAlive="1" name="query (10)" type="5" refreshedVersion="8" minRefreshableVersion="3" saveData="1">
     <dbPr connection="Provider=Microsoft.Office.List.OLEDB.2.0;Data Source=&quot;&quot;;ApplicationName=Excel;Version=12.0.0.0" command="&lt;LIST&gt;&lt;VIEWGUID&gt;4B095B6C-E238-4145-AEAC-58FC81495ECD&lt;/VIEWGUID&gt;&lt;LISTNAME&gt;7043100c-5b9c-457f-ab38-a4bb8df4a390&lt;/LISTNAME&gt;&lt;LISTWEB&gt;https://groupefnac.sharepoint.com/sites/SAVVY_FNACDARTY/_vti_bin&lt;/LISTWEB&gt;&lt;LISTSUBWEB&gt;&lt;/LISTSUBWEB&gt;&lt;ROOTFOLDER&gt;/sites/SAVVY%5fFNACDARTY/Documents%20partages/KitchenAid&lt;/ROOTFOLDER&gt;&lt;/LIST&gt;" commandType="5"/>
   </connection>
 </connections>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1046" uniqueCount="300">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1086" uniqueCount="310">
   <si>
     <t>Modifié</t>
   </si>
@@ -156,6 +156,9 @@
     <t>sites/SAVVY_FNACDARTY/Documents partages/KitchenAid/Invoicing</t>
   </si>
   <si>
+    <t>sites/SAVVY_FNACDARTY/Documents partages/KitchenAid/Owner Manual</t>
+  </si>
+  <si>
     <t>sites/SAVVY_FNACDARTY/Documents partages/KitchenAid/Pricelist</t>
   </si>
   <si>
@@ -183,6 +186,9 @@
     <t>Invoicing</t>
   </si>
   <si>
+    <t>Owner Manual</t>
+  </si>
+  <si>
     <t>PlayBook Service - Europe.pptx</t>
   </si>
   <si>
@@ -372,6 +378,9 @@
     <t>5KSM185PS.pdf</t>
   </si>
   <si>
+    <t>5KSM185PSBBK.pdf</t>
+  </si>
+  <si>
     <t>5KSM193AD.pdf</t>
   </si>
   <si>
@@ -795,6 +804,9 @@
     <t>5KHBV83E.pdf</t>
   </si>
   <si>
+    <t>KHBRV71BM0.pdf</t>
+  </si>
+  <si>
     <t>5KHM5110.pdf</t>
   </si>
   <si>
@@ -888,6 +900,21 @@
     <t>5KES8452BBM.pdf</t>
   </si>
   <si>
+    <t>5KES8453BBM.pdf</t>
+  </si>
+  <si>
+    <t>5KES8453EPL.pdf</t>
+  </si>
+  <si>
+    <t>5KES8454BBM.pdf</t>
+  </si>
+  <si>
+    <t>5KES8454EBM.pdf</t>
+  </si>
+  <si>
+    <t>5KES8454EPL.pdf</t>
+  </si>
+  <si>
     <t>5KES8556E.pdf</t>
   </si>
   <si>
@@ -898,6 +925,9 @@
   </si>
   <si>
     <t>PEX_Template-SEC.xlsx</t>
+  </si>
+  <si>
+    <t>owners-manual-W10506838-RevB.pdf</t>
   </si>
   <si>
     <t>Spare Part Pricelist 2026 - USD.xlsx</t>
@@ -1508,7 +1538,7 @@
 </file>
 
 <file path=xl/queryTables/queryTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="query (10)" backgroundRefresh="0" connectionId="1" xr16:uid="{AC7DAECE-BD54-460A-9326-0D0B6CF545C6}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0">
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="query (10)" backgroundRefresh="0" connectionId="1" xr16:uid="{5C35AC1A-9946-4106-8F72-08D6EAC615CE}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0">
   <queryTableRefresh nextId="7">
     <queryTableFields count="6">
       <queryTableField id="6" name="Nom" tableColumnId="1"/>
@@ -1523,15 +1553,15 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{29695AED-BAA2-44CF-923A-8DC450594E3B}" name="Tableau_query__10" displayName="Tableau_query__10" ref="A1:F261" tableType="queryTable" totalsRowShown="0">
-  <autoFilter ref="A1:F261" xr:uid="{29695AED-BAA2-44CF-923A-8DC450594E3B}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{FE251108-4349-4985-8CC5-00A231624740}" name="Tableau_query__10" displayName="Tableau_query__10" ref="A1:F271" tableType="queryTable" totalsRowShown="0">
+  <autoFilter ref="A1:F271" xr:uid="{FE251108-4349-4985-8CC5-00A231624740}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{FD23D889-8698-4F88-BABA-45D7711B45A4}" uniqueName="FileLeafRef" name="Nom" queryTableFieldId="6"/>
-    <tableColumn id="2" xr3:uid="{F504DEB1-323D-479A-80A9-373D86D266DC}" uniqueName="Modified" name="Modifié" queryTableFieldId="1" dataDxfId="4"/>
-    <tableColumn id="3" xr3:uid="{559FDCAB-9436-4B56-962A-2C70A6B15DEE}" uniqueName="Editor" name="Modifié par" queryTableFieldId="3" dataDxfId="3"/>
-    <tableColumn id="4" xr3:uid="{06555F81-506D-437D-9BBB-F9EC299D73B8}" uniqueName="_x005f_x0024_Resources_x005f_x003a_core_x005f_x002c_Signoff_Status" name="État de validation" queryTableFieldId="2" dataDxfId="2"/>
-    <tableColumn id="5" xr3:uid="{23E5CF56-3194-4A92-9B33-3825EE41DBF8}" uniqueName="FSObjType" name="Type d'élément" queryTableFieldId="5" dataDxfId="1"/>
-    <tableColumn id="6" xr3:uid="{E795883B-1886-4DA4-AF55-D148B00997C2}" uniqueName="FileDirRef" name="Chemin d'accès" queryTableFieldId="4" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{8C0DA7BD-B772-48C4-9D5F-D7A77DFE023D}" uniqueName="FileLeafRef" name="Nom" queryTableFieldId="6"/>
+    <tableColumn id="2" xr3:uid="{EB4B6F69-24BC-4053-A755-5DEA4C1EAB9E}" uniqueName="Modified" name="Modifié" queryTableFieldId="1" dataDxfId="4"/>
+    <tableColumn id="3" xr3:uid="{D8D97B05-3AA6-4392-87C6-079CE1BCB7AB}" uniqueName="Editor" name="Modifié par" queryTableFieldId="3" dataDxfId="3"/>
+    <tableColumn id="4" xr3:uid="{266448A2-8B36-44B2-8F8F-90DF12E43E7F}" uniqueName="_x005f_x0024_Resources_x005f_x003a_core_x005f_x002c_Signoff_Status" name="État de validation" queryTableFieldId="2" dataDxfId="2"/>
+    <tableColumn id="5" xr3:uid="{D9FB2965-A87A-4329-8EDA-BF044DECA255}" uniqueName="FSObjType" name="Type d'élément" queryTableFieldId="5" dataDxfId="1"/>
+    <tableColumn id="6" xr3:uid="{1D1A4FBF-3331-424E-B200-5D4053268E06}" uniqueName="FileDirRef" name="Chemin d'accès" queryTableFieldId="4" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1853,8 +1883,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15282A11-C47C-4027-91DA-BEB9E3623C78}">
-  <dimension ref="A1:F261"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{930B7203-5CF6-415F-96AB-889F2253643F}">
+  <dimension ref="A1:F271"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="51.33203125" bestFit="1" customWidth="1"/>
@@ -1887,7 +1917,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B2" s="2">
         <v>46238.717141203706</v>
@@ -1905,7 +1935,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B3" s="2">
         <v>46238.717141203706</v>
@@ -1923,7 +1953,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B4" s="2">
         <v>46238.717141203706</v>
@@ -1941,17 +1971,17 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B5" s="2">
-        <v>46238.717164351852</v>
+        <v>46296.489085648151</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>7</v>
@@ -1959,10 +1989,10 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B6" s="2">
-        <v>46238.717175925929</v>
+        <v>46296.48909722222</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>6</v>
@@ -1977,17 +2007,17 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B7" s="2">
-        <v>46238.717141203706</v>
+        <v>46238.717175925929</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F7" s="4" t="s">
         <v>7</v>
@@ -1995,7 +2025,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B8" s="2">
         <v>46238.717141203706</v>
@@ -2013,7 +2043,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B9" s="2">
         <v>46238.717141203706</v>
@@ -2031,7 +2061,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B10" s="2">
         <v>46238.717141203706</v>
@@ -2049,7 +2079,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B11" s="2">
         <v>46238.717141203706</v>
@@ -2067,7 +2097,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B12" s="2">
         <v>46238.717141203706</v>
@@ -2085,43 +2115,43 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B13" s="2">
-        <v>46238.717268518521</v>
+        <v>46238.717141203706</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B14" s="2">
-        <v>46238.717141203706</v>
+        <v>46296.489074074074</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B15" s="2">
         <v>46238.717141203706</v>
@@ -2139,7 +2169,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B16" s="2">
         <v>46238.717141203706</v>
@@ -2157,7 +2187,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B17" s="2">
         <v>46238.717141203706</v>
@@ -2175,7 +2205,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B18" s="2">
         <v>46238.717141203706</v>
@@ -2193,7 +2223,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B19" s="2">
         <v>46238.717141203706</v>
@@ -2211,7 +2241,7 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B20" s="2">
         <v>46238.717141203706</v>
@@ -2229,7 +2259,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B21" s="2">
         <v>46238.717141203706</v>
@@ -2247,10 +2277,10 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B22" s="2">
-        <v>46238.717152777775</v>
+        <v>46238.717141203706</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>6</v>
@@ -2265,7 +2295,7 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B23" s="2">
         <v>46238.717152777775</v>
@@ -2283,7 +2313,7 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B24" s="2">
         <v>46238.717152777775</v>
@@ -2301,7 +2331,7 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B25" s="2">
         <v>46238.717152777775</v>
@@ -2319,7 +2349,7 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B26" s="2">
         <v>46238.717152777775</v>
@@ -2337,7 +2367,7 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B27" s="2">
         <v>46238.717152777775</v>
@@ -2355,7 +2385,7 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B28" s="2">
         <v>46238.717152777775</v>
@@ -2373,7 +2403,7 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B29" s="2">
         <v>46238.717152777775</v>
@@ -2391,7 +2421,7 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B30" s="2">
         <v>46238.717152777775</v>
@@ -2404,12 +2434,12 @@
         <v>8</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B31" s="2">
         <v>46238.717152777775</v>
@@ -2427,7 +2457,7 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B32" s="2">
         <v>46238.717152777775</v>
@@ -2445,25 +2475,25 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B33" s="2">
-        <v>46238.717662037037</v>
+        <v>46238.717152777775</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D33" s="4"/>
       <c r="E33" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B34" s="2">
         <v>46238.717662037037</v>
@@ -2481,7 +2511,7 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B35" s="2">
         <v>46238.717662037037</v>
@@ -2499,7 +2529,7 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B36" s="2">
         <v>46238.717662037037</v>
@@ -2517,7 +2547,7 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B37" s="2">
         <v>46238.717662037037</v>
@@ -2535,10 +2565,10 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B38" s="2">
-        <v>46238.717685185184</v>
+        <v>46238.717662037037</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>6</v>
@@ -2553,10 +2583,10 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B39" s="2">
-        <v>46238.717673611114</v>
+        <v>46238.717685185184</v>
       </c>
       <c r="C39" s="3" t="s">
         <v>6</v>
@@ -2571,7 +2601,7 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B40" s="2">
         <v>46238.717673611114</v>
@@ -2589,10 +2619,10 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B41" s="2">
-        <v>46238.717685185184</v>
+        <v>46238.717673611114</v>
       </c>
       <c r="C41" s="3" t="s">
         <v>6</v>
@@ -2607,7 +2637,7 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B42" s="2">
         <v>46238.717685185184</v>
@@ -2625,7 +2655,7 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B43" s="2">
         <v>46238.717685185184</v>
@@ -2643,7 +2673,7 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B44" s="2">
         <v>46238.717685185184</v>
@@ -2661,7 +2691,7 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B45" s="2">
         <v>46238.717685185184</v>
@@ -2679,7 +2709,7 @@
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B46" s="2">
         <v>46238.717685185184</v>
@@ -2697,10 +2727,10 @@
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B47" s="2">
-        <v>46238.71769675926</v>
+        <v>46238.717685185184</v>
       </c>
       <c r="C47" s="3" t="s">
         <v>6</v>
@@ -2715,7 +2745,7 @@
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B48" s="2">
         <v>46238.71769675926</v>
@@ -2733,7 +2763,7 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B49" s="2">
         <v>46238.71769675926</v>
@@ -2751,10 +2781,10 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B50" s="2">
-        <v>46238.71770833333</v>
+        <v>46238.71769675926</v>
       </c>
       <c r="C50" s="3" t="s">
         <v>6</v>
@@ -2769,10 +2799,10 @@
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B51" s="2">
-        <v>46238.717719907407</v>
+        <v>46238.71770833333</v>
       </c>
       <c r="C51" s="3" t="s">
         <v>6</v>
@@ -2782,15 +2812,15 @@
         <v>9</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B52" s="2">
-        <v>46238.71770833333</v>
+        <v>46238.717719907407</v>
       </c>
       <c r="C52" s="3" t="s">
         <v>6</v>
@@ -2805,7 +2835,7 @@
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B53" s="2">
         <v>46238.71770833333</v>
@@ -2823,10 +2853,10 @@
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B54" s="2">
-        <v>46238.717731481483</v>
+        <v>46238.71770833333</v>
       </c>
       <c r="C54" s="3" t="s">
         <v>6</v>
@@ -2841,10 +2871,10 @@
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B55" s="2">
-        <v>46238.717719907407</v>
+        <v>46238.717731481483</v>
       </c>
       <c r="C55" s="3" t="s">
         <v>6</v>
@@ -2859,7 +2889,7 @@
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B56" s="2">
         <v>46238.717719907407</v>
@@ -2877,10 +2907,10 @@
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B57" s="2">
-        <v>46238.717731481483</v>
+        <v>46238.717719907407</v>
       </c>
       <c r="C57" s="3" t="s">
         <v>6</v>
@@ -2895,7 +2925,7 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B58" s="2">
         <v>46238.717731481483</v>
@@ -2913,10 +2943,10 @@
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B59" s="2">
-        <v>46238.717743055553</v>
+        <v>46238.717731481483</v>
       </c>
       <c r="C59" s="3" t="s">
         <v>6</v>
@@ -2931,7 +2961,7 @@
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B60" s="2">
         <v>46238.717743055553</v>
@@ -2949,7 +2979,7 @@
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B61" s="2">
         <v>46238.717743055553</v>
@@ -2967,7 +2997,7 @@
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B62" s="2">
         <v>46238.717743055553</v>
@@ -2985,7 +3015,7 @@
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B63" s="2">
         <v>46238.717743055553</v>
@@ -3003,7 +3033,7 @@
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B64" s="2">
         <v>46238.717743055553</v>
@@ -3021,7 +3051,7 @@
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B65" s="2">
         <v>46238.717743055553</v>
@@ -3039,10 +3069,10 @@
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B66" s="2">
-        <v>46238.71775462963</v>
+        <v>46238.717743055553</v>
       </c>
       <c r="C66" s="3" t="s">
         <v>6</v>
@@ -3057,10 +3087,10 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B67" s="2">
-        <v>46238.717766203707</v>
+        <v>46238.71775462963</v>
       </c>
       <c r="C67" s="3" t="s">
         <v>6</v>
@@ -3075,10 +3105,10 @@
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B68" s="2">
-        <v>46238.71775462963</v>
+        <v>46238.717766203707</v>
       </c>
       <c r="C68" s="3" t="s">
         <v>6</v>
@@ -3093,10 +3123,10 @@
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B69" s="2">
-        <v>46238.717766203707</v>
+        <v>46296.489074074074</v>
       </c>
       <c r="C69" s="3" t="s">
         <v>6</v>
@@ -3111,10 +3141,10 @@
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B70" s="2">
-        <v>46238.717766203707</v>
+        <v>46238.71775462963</v>
       </c>
       <c r="C70" s="3" t="s">
         <v>6</v>
@@ -3129,10 +3159,10 @@
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A71" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B71" s="2">
-        <v>46238.717777777776</v>
+        <v>46238.717766203707</v>
       </c>
       <c r="C71" s="3" t="s">
         <v>6</v>
@@ -3147,7 +3177,7 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B72" s="2">
         <v>46238.717766203707</v>
@@ -3165,7 +3195,7 @@
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B73" s="2">
         <v>46238.717777777776</v>
@@ -3183,10 +3213,10 @@
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B74" s="2">
-        <v>46238.717777777776</v>
+        <v>46238.717766203707</v>
       </c>
       <c r="C74" s="3" t="s">
         <v>6</v>
@@ -3201,7 +3231,7 @@
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A75" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B75" s="2">
         <v>46238.717777777776</v>
@@ -3219,10 +3249,10 @@
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A76" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B76" s="2">
-        <v>46238.717789351853</v>
+        <v>46238.717777777776</v>
       </c>
       <c r="C76" s="3" t="s">
         <v>6</v>
@@ -3237,7 +3267,7 @@
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A77" s="1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B77" s="2">
         <v>46238.717777777776</v>
@@ -3255,7 +3285,7 @@
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A78" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B78" s="2">
         <v>46238.717789351853</v>
@@ -3273,10 +3303,10 @@
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A79" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B79" s="2">
-        <v>46238.717789351853</v>
+        <v>46238.717777777776</v>
       </c>
       <c r="C79" s="3" t="s">
         <v>6</v>
@@ -3291,7 +3321,7 @@
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A80" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B80" s="2">
         <v>46238.717789351853</v>
@@ -3309,10 +3339,10 @@
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A81" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B81" s="2">
-        <v>46238.717800925922</v>
+        <v>46238.717789351853</v>
       </c>
       <c r="C81" s="3" t="s">
         <v>6</v>
@@ -3327,10 +3357,10 @@
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A82" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B82" s="2">
-        <v>46238.717800925922</v>
+        <v>46238.717789351853</v>
       </c>
       <c r="C82" s="3" t="s">
         <v>6</v>
@@ -3345,7 +3375,7 @@
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A83" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B83" s="2">
         <v>46238.717800925922</v>
@@ -3363,10 +3393,10 @@
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A84" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B84" s="2">
-        <v>46238.717812499999</v>
+        <v>46238.717800925922</v>
       </c>
       <c r="C84" s="3" t="s">
         <v>6</v>
@@ -3381,10 +3411,10 @@
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A85" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B85" s="2">
-        <v>46238.717812499999</v>
+        <v>46238.717800925922</v>
       </c>
       <c r="C85" s="3" t="s">
         <v>6</v>
@@ -3399,7 +3429,7 @@
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A86" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B86" s="2">
         <v>46238.717812499999</v>
@@ -3417,10 +3447,10 @@
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A87" s="1" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B87" s="2">
-        <v>46238.717858796299</v>
+        <v>46238.717812499999</v>
       </c>
       <c r="C87" s="3" t="s">
         <v>6</v>
@@ -3430,15 +3460,15 @@
         <v>9</v>
       </c>
       <c r="F87" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A88" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B88" s="2">
-        <v>46238.717858796299</v>
+        <v>46238.717812499999</v>
       </c>
       <c r="C88" s="3" t="s">
         <v>6</v>
@@ -3448,15 +3478,15 @@
         <v>9</v>
       </c>
       <c r="F88" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A89" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B89" s="2">
-        <v>46238.717442129629</v>
+        <v>46238.717858796299</v>
       </c>
       <c r="C89" s="3" t="s">
         <v>6</v>
@@ -3466,15 +3496,15 @@
         <v>9</v>
       </c>
       <c r="F89" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A90" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B90" s="2">
-        <v>46238.717453703706</v>
+        <v>46238.717858796299</v>
       </c>
       <c r="C90" s="3" t="s">
         <v>6</v>
@@ -3484,15 +3514,15 @@
         <v>9</v>
       </c>
       <c r="F90" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A91" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B91" s="2">
-        <v>46238.717453703706</v>
+        <v>46238.717442129629</v>
       </c>
       <c r="C91" s="3" t="s">
         <v>6</v>
@@ -3507,10 +3537,10 @@
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A92" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B92" s="2">
-        <v>46238.717465277776</v>
+        <v>46238.717453703706</v>
       </c>
       <c r="C92" s="3" t="s">
         <v>6</v>
@@ -3525,10 +3555,10 @@
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A93" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B93" s="2">
-        <v>46238.717465277776</v>
+        <v>46238.717453703706</v>
       </c>
       <c r="C93" s="3" t="s">
         <v>6</v>
@@ -3543,7 +3573,7 @@
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A94" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B94" s="2">
         <v>46238.717465277776</v>
@@ -3561,7 +3591,7 @@
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A95" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B95" s="2">
         <v>46238.717465277776</v>
@@ -3579,7 +3609,7 @@
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A96" s="1" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B96" s="2">
         <v>46238.717465277776</v>
@@ -3597,7 +3627,7 @@
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A97" s="1" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B97" s="2">
         <v>46238.717465277776</v>
@@ -3615,7 +3645,7 @@
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A98" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B98" s="2">
         <v>46238.717465277776</v>
@@ -3633,10 +3663,10 @@
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A99" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B99" s="2">
-        <v>46238.717476851853</v>
+        <v>46238.717465277776</v>
       </c>
       <c r="C99" s="3" t="s">
         <v>6</v>
@@ -3651,10 +3681,10 @@
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A100" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B100" s="2">
-        <v>46238.717476851853</v>
+        <v>46238.717465277776</v>
       </c>
       <c r="C100" s="3" t="s">
         <v>6</v>
@@ -3669,7 +3699,7 @@
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A101" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B101" s="2">
         <v>46238.717476851853</v>
@@ -3687,7 +3717,7 @@
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A102" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B102" s="2">
         <v>46238.717476851853</v>
@@ -3705,7 +3735,7 @@
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A103" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B103" s="2">
         <v>46238.717476851853</v>
@@ -3723,7 +3753,7 @@
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A104" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B104" s="2">
         <v>46238.717476851853</v>
@@ -3741,10 +3771,10 @@
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A105" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B105" s="2">
-        <v>46238.717488425929</v>
+        <v>46238.717476851853</v>
       </c>
       <c r="C105" s="3" t="s">
         <v>6</v>
@@ -3759,10 +3789,10 @@
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A106" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B106" s="2">
-        <v>46238.717488425929</v>
+        <v>46238.717476851853</v>
       </c>
       <c r="C106" s="3" t="s">
         <v>6</v>
@@ -3777,10 +3807,10 @@
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A107" s="1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B107" s="2">
-        <v>46238.717499999999</v>
+        <v>46238.717488425929</v>
       </c>
       <c r="C107" s="3" t="s">
         <v>6</v>
@@ -3795,7 +3825,7 @@
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A108" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B108" s="2">
         <v>46238.717488425929</v>
@@ -3813,10 +3843,10 @@
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A109" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B109" s="2">
-        <v>46238.717488425929</v>
+        <v>46238.717499999999</v>
       </c>
       <c r="C109" s="3" t="s">
         <v>6</v>
@@ -3831,7 +3861,7 @@
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A110" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B110" s="2">
         <v>46238.717488425929</v>
@@ -3849,10 +3879,10 @@
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A111" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B111" s="2">
-        <v>46238.717499999999</v>
+        <v>46238.717488425929</v>
       </c>
       <c r="C111" s="3" t="s">
         <v>6</v>
@@ -3867,17 +3897,17 @@
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A112" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B112" s="2">
-        <v>46238.717152777775</v>
+        <v>46238.717488425929</v>
       </c>
       <c r="C112" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D112" s="4"/>
       <c r="E112" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F112" s="4" t="s">
         <v>16</v>
@@ -3885,7 +3915,7 @@
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A113" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B113" s="2">
         <v>46238.717499999999</v>
@@ -3903,17 +3933,17 @@
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A114" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B114" s="2">
-        <v>46238.717499999999</v>
+        <v>46238.717152777775</v>
       </c>
       <c r="C114" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D114" s="4"/>
       <c r="E114" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F114" s="4" t="s">
         <v>16</v>
@@ -3921,17 +3951,17 @@
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A115" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B115" s="2">
-        <v>46238.717152777775</v>
+        <v>46238.717499999999</v>
       </c>
       <c r="C115" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D115" s="4"/>
       <c r="E115" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F115" s="4" t="s">
         <v>16</v>
@@ -3939,17 +3969,17 @@
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A116" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B116" s="2">
-        <v>46238.717152777775</v>
+        <v>46238.717499999999</v>
       </c>
       <c r="C116" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D116" s="4"/>
       <c r="E116" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F116" s="4" t="s">
         <v>16</v>
@@ -3957,46 +3987,46 @@
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A117" s="1" t="s">
-        <v>143</v>
+        <v>163</v>
       </c>
       <c r="B117" s="2">
-        <v>46238.717858796299</v>
+        <v>46238.717152777775</v>
       </c>
       <c r="C117" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D117" s="4"/>
       <c r="E117" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F117" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A118" s="1" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B118" s="2">
-        <v>46238.717835648145</v>
+        <v>46238.717152777775</v>
       </c>
       <c r="C118" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D118" s="4"/>
       <c r="E118" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F118" s="4" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A119" s="1" t="s">
-        <v>163</v>
+        <v>146</v>
       </c>
       <c r="B119" s="2">
-        <v>46238.717835648145</v>
+        <v>46238.717858796299</v>
       </c>
       <c r="C119" s="3" t="s">
         <v>6</v>
@@ -4006,12 +4036,12 @@
         <v>9</v>
       </c>
       <c r="F119" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A120" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B120" s="2">
         <v>46238.717835648145</v>
@@ -4029,7 +4059,7 @@
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A121" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B121" s="2">
         <v>46238.717835648145</v>
@@ -4047,10 +4077,10 @@
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A122" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B122" s="2">
-        <v>46238.717847222222</v>
+        <v>46238.717835648145</v>
       </c>
       <c r="C122" s="3" t="s">
         <v>6</v>
@@ -4065,10 +4095,10 @@
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A123" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B123" s="2">
-        <v>46238.717858796299</v>
+        <v>46238.717835648145</v>
       </c>
       <c r="C123" s="3" t="s">
         <v>6</v>
@@ -4078,15 +4108,15 @@
         <v>9</v>
       </c>
       <c r="F123" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A124" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B124" s="2">
-        <v>46238.717858796299</v>
+        <v>46238.717847222222</v>
       </c>
       <c r="C124" s="3" t="s">
         <v>6</v>
@@ -4096,15 +4126,15 @@
         <v>9</v>
       </c>
       <c r="F124" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A125" s="1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B125" s="2">
-        <v>46238.717349537037</v>
+        <v>46238.717858796299</v>
       </c>
       <c r="C125" s="3" t="s">
         <v>6</v>
@@ -4114,15 +4144,15 @@
         <v>9</v>
       </c>
       <c r="F125" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A126" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B126" s="2">
-        <v>46238.717349537037</v>
+        <v>46238.717858796299</v>
       </c>
       <c r="C126" s="3" t="s">
         <v>6</v>
@@ -4132,12 +4162,12 @@
         <v>9</v>
       </c>
       <c r="F126" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A127" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B127" s="2">
         <v>46238.717349537037</v>
@@ -4155,10 +4185,10 @@
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A128" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B128" s="2">
-        <v>46238.717372685183</v>
+        <v>46238.717349537037</v>
       </c>
       <c r="C128" s="3" t="s">
         <v>6</v>
@@ -4173,10 +4203,10 @@
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A129" s="1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B129" s="2">
-        <v>46238.717361111114</v>
+        <v>46238.717349537037</v>
       </c>
       <c r="C129" s="3" t="s">
         <v>6</v>
@@ -4191,10 +4221,10 @@
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A130" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B130" s="2">
-        <v>46238.717361111114</v>
+        <v>46238.717372685183</v>
       </c>
       <c r="C130" s="3" t="s">
         <v>6</v>
@@ -4209,10 +4239,10 @@
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A131" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B131" s="2">
-        <v>46238.717372685183</v>
+        <v>46238.717361111114</v>
       </c>
       <c r="C131" s="3" t="s">
         <v>6</v>
@@ -4227,10 +4257,10 @@
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A132" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B132" s="2">
-        <v>46238.717372685183</v>
+        <v>46238.717361111114</v>
       </c>
       <c r="C132" s="3" t="s">
         <v>6</v>
@@ -4245,10 +4275,10 @@
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A133" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B133" s="2">
-        <v>46238.71738425926</v>
+        <v>46238.717372685183</v>
       </c>
       <c r="C133" s="3" t="s">
         <v>6</v>
@@ -4263,7 +4293,7 @@
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A134" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B134" s="2">
         <v>46238.717372685183</v>
@@ -4281,7 +4311,7 @@
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A135" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B135" s="2">
         <v>46238.71738425926</v>
@@ -4299,10 +4329,10 @@
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A136" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B136" s="2">
-        <v>46238.717395833337</v>
+        <v>46238.717372685183</v>
       </c>
       <c r="C136" s="3" t="s">
         <v>6</v>
@@ -4317,7 +4347,7 @@
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A137" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B137" s="2">
         <v>46238.71738425926</v>
@@ -4335,10 +4365,10 @@
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A138" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B138" s="2">
-        <v>46238.71738425926</v>
+        <v>46238.717395833337</v>
       </c>
       <c r="C138" s="3" t="s">
         <v>6</v>
@@ -4353,10 +4383,10 @@
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A139" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B139" s="2">
-        <v>46238.717395833337</v>
+        <v>46238.71738425926</v>
       </c>
       <c r="C139" s="3" t="s">
         <v>6</v>
@@ -4371,10 +4401,10 @@
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A140" s="1" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B140" s="2">
-        <v>46238.717407407406</v>
+        <v>46238.71738425926</v>
       </c>
       <c r="C140" s="3" t="s">
         <v>6</v>
@@ -4389,7 +4419,7 @@
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A141" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B141" s="2">
         <v>46238.717395833337</v>
@@ -4407,10 +4437,10 @@
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A142" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B142" s="2">
-        <v>46238.717395833337</v>
+        <v>46238.717407407406</v>
       </c>
       <c r="C142" s="3" t="s">
         <v>6</v>
@@ -4425,10 +4455,10 @@
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A143" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B143" s="2">
-        <v>46238.717418981483</v>
+        <v>46238.717395833337</v>
       </c>
       <c r="C143" s="3" t="s">
         <v>6</v>
@@ -4443,10 +4473,10 @@
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A144" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B144" s="2">
-        <v>46238.717407407406</v>
+        <v>46238.717395833337</v>
       </c>
       <c r="C144" s="3" t="s">
         <v>6</v>
@@ -4461,7 +4491,7 @@
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A145" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B145" s="2">
         <v>46238.717418981483</v>
@@ -4479,10 +4509,10 @@
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A146" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B146" s="2">
-        <v>46238.717430555553</v>
+        <v>46238.717407407406</v>
       </c>
       <c r="C146" s="3" t="s">
         <v>6</v>
@@ -4497,10 +4527,10 @@
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A147" s="1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B147" s="2">
-        <v>46238.717430555553</v>
+        <v>46238.717418981483</v>
       </c>
       <c r="C147" s="3" t="s">
         <v>6</v>
@@ -4515,10 +4545,10 @@
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A148" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B148" s="2">
-        <v>46238.717442129629</v>
+        <v>46238.717430555553</v>
       </c>
       <c r="C148" s="3" t="s">
         <v>6</v>
@@ -4533,10 +4563,10 @@
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A149" s="1" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B149" s="2">
-        <v>46238.717291666668</v>
+        <v>46238.717430555553</v>
       </c>
       <c r="C149" s="3" t="s">
         <v>6</v>
@@ -4546,15 +4576,15 @@
         <v>9</v>
       </c>
       <c r="F149" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A150" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B150" s="2">
-        <v>46238.717291666668</v>
+        <v>46238.717442129629</v>
       </c>
       <c r="C150" s="3" t="s">
         <v>6</v>
@@ -4564,12 +4594,12 @@
         <v>9</v>
       </c>
       <c r="F150" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A151" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B151" s="2">
         <v>46238.717291666668</v>
@@ -4587,10 +4617,10 @@
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A152" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B152" s="2">
-        <v>46238.717303240737</v>
+        <v>46238.717291666668</v>
       </c>
       <c r="C152" s="3" t="s">
         <v>6</v>
@@ -4605,17 +4635,17 @@
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A153" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B153" s="2">
-        <v>46238.717152777775</v>
+        <v>46238.717291666668</v>
       </c>
       <c r="C153" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D153" s="4"/>
       <c r="E153" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F153" s="4" t="s">
         <v>21</v>
@@ -4623,10 +4653,10 @@
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A154" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B154" s="2">
-        <v>46238.717847222222</v>
+        <v>46238.717303240737</v>
       </c>
       <c r="C154" s="3" t="s">
         <v>6</v>
@@ -4636,33 +4666,33 @@
         <v>9</v>
       </c>
       <c r="F154" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A155" s="1" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B155" s="2">
-        <v>46238.717303240737</v>
+        <v>46238.717152777775</v>
       </c>
       <c r="C155" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D155" s="4"/>
       <c r="E155" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F155" s="4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A156" s="1" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B156" s="2">
-        <v>46238.717303240737</v>
+        <v>46238.717847222222</v>
       </c>
       <c r="C156" s="3" t="s">
         <v>6</v>
@@ -4672,12 +4702,12 @@
         <v>9</v>
       </c>
       <c r="F156" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A157" s="1" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B157" s="2">
         <v>46238.717303240737</v>
@@ -4695,7 +4725,7 @@
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A158" s="1" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B158" s="2">
         <v>46238.717303240737</v>
@@ -4713,10 +4743,10 @@
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A159" s="1" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B159" s="2">
-        <v>46238.717314814814</v>
+        <v>46238.717303240737</v>
       </c>
       <c r="C159" s="3" t="s">
         <v>6</v>
@@ -4731,10 +4761,10 @@
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A160" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B160" s="2">
-        <v>46238.717326388891</v>
+        <v>46238.717303240737</v>
       </c>
       <c r="C160" s="3" t="s">
         <v>6</v>
@@ -4749,10 +4779,10 @@
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A161" s="1" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B161" s="2">
-        <v>46238.717326388891</v>
+        <v>46238.717314814814</v>
       </c>
       <c r="C161" s="3" t="s">
         <v>6</v>
@@ -4767,10 +4797,10 @@
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A162" s="1" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B162" s="2">
-        <v>46238.717314814814</v>
+        <v>46238.717326388891</v>
       </c>
       <c r="C162" s="3" t="s">
         <v>6</v>
@@ -4785,7 +4815,7 @@
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A163" s="1" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B163" s="2">
         <v>46238.717326388891</v>
@@ -4803,10 +4833,10 @@
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A164" s="1" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B164" s="2">
-        <v>46238.717326388891</v>
+        <v>46238.717314814814</v>
       </c>
       <c r="C164" s="3" t="s">
         <v>6</v>
@@ -4821,10 +4851,10 @@
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A165" s="1" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B165" s="2">
-        <v>46238.71733796296</v>
+        <v>46238.717326388891</v>
       </c>
       <c r="C165" s="3" t="s">
         <v>6</v>
@@ -4839,17 +4869,17 @@
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A166" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B166" s="2">
-        <v>46238.717152777775</v>
+        <v>46238.717326388891</v>
       </c>
       <c r="C166" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D166" s="4"/>
       <c r="E166" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F166" s="4" t="s">
         <v>23</v>
@@ -4857,10 +4887,10 @@
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A167" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B167" s="2">
-        <v>46238.717326388891</v>
+        <v>46238.71733796296</v>
       </c>
       <c r="C167" s="3" t="s">
         <v>6</v>
@@ -4875,28 +4905,28 @@
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A168" s="1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B168" s="2">
-        <v>46238.717824074076</v>
+        <v>46238.717152777775</v>
       </c>
       <c r="C168" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D168" s="4"/>
       <c r="E168" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F168" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A169" s="1" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B169" s="2">
-        <v>46238.717835648145</v>
+        <v>46238.717326388891</v>
       </c>
       <c r="C169" s="3" t="s">
         <v>6</v>
@@ -4906,12 +4936,12 @@
         <v>9</v>
       </c>
       <c r="F169" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A170" s="1" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B170" s="2">
         <v>46238.717824074076</v>
@@ -4929,7 +4959,7 @@
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A171" s="1" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B171" s="2">
         <v>46238.717835648145</v>
@@ -4947,10 +4977,10 @@
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A172" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B172" s="2">
-        <v>46238.717835648145</v>
+        <v>46238.717824074076</v>
       </c>
       <c r="C172" s="3" t="s">
         <v>6</v>
@@ -4965,10 +4995,10 @@
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A173" s="1" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B173" s="2">
-        <v>46238.717326388891</v>
+        <v>46238.717835648145</v>
       </c>
       <c r="C173" s="3" t="s">
         <v>6</v>
@@ -4978,15 +5008,15 @@
         <v>9</v>
       </c>
       <c r="F173" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A174" s="1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B174" s="2">
-        <v>46238.71733796296</v>
+        <v>46238.717835648145</v>
       </c>
       <c r="C174" s="3" t="s">
         <v>6</v>
@@ -4996,15 +5026,15 @@
         <v>9</v>
       </c>
       <c r="F174" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A175" s="1" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B175" s="2">
-        <v>46238.71733796296</v>
+        <v>46238.717326388891</v>
       </c>
       <c r="C175" s="3" t="s">
         <v>6</v>
@@ -5019,7 +5049,7 @@
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A176" s="1" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B176" s="2">
         <v>46238.71733796296</v>
@@ -5037,7 +5067,7 @@
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A177" s="1" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B177" s="2">
         <v>46238.71733796296</v>
@@ -5055,7 +5085,7 @@
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A178" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B178" s="2">
         <v>46238.71733796296</v>
@@ -5073,10 +5103,10 @@
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A179" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B179" s="2">
-        <v>46238.717349537037</v>
+        <v>46238.71733796296</v>
       </c>
       <c r="C179" s="3" t="s">
         <v>6</v>
@@ -5091,10 +5121,10 @@
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A180" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B180" s="2">
-        <v>46238.717349537037</v>
+        <v>46238.71733796296</v>
       </c>
       <c r="C180" s="3" t="s">
         <v>6</v>
@@ -5109,7 +5139,7 @@
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A181" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B181" s="2">
         <v>46238.717349537037</v>
@@ -5127,10 +5157,10 @@
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A182" s="1" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B182" s="2">
-        <v>46238.717442129629</v>
+        <v>46238.717349537037</v>
       </c>
       <c r="C182" s="3" t="s">
         <v>6</v>
@@ -5140,15 +5170,15 @@
         <v>9</v>
       </c>
       <c r="F182" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A183" s="1" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B183" s="2">
-        <v>46238.717442129629</v>
+        <v>46238.717349537037</v>
       </c>
       <c r="C183" s="3" t="s">
         <v>6</v>
@@ -5158,12 +5188,12 @@
         <v>9</v>
       </c>
       <c r="F183" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A184" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B184" s="2">
         <v>46238.717442129629</v>
@@ -5181,7 +5211,7 @@
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A185" s="1" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B185" s="2">
         <v>46238.717442129629</v>
@@ -5199,7 +5229,7 @@
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A186" s="1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B186" s="2">
         <v>46238.717442129629</v>
@@ -5217,10 +5247,10 @@
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A187" s="1" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B187" s="2">
-        <v>46238.717499999999</v>
+        <v>46238.717442129629</v>
       </c>
       <c r="C187" s="3" t="s">
         <v>6</v>
@@ -5230,15 +5260,15 @@
         <v>9</v>
       </c>
       <c r="F187" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A188" s="1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B188" s="2">
-        <v>46238.717499999999</v>
+        <v>46238.717442129629</v>
       </c>
       <c r="C188" s="3" t="s">
         <v>6</v>
@@ -5248,15 +5278,15 @@
         <v>9</v>
       </c>
       <c r="F188" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A189" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B189" s="2">
-        <v>46238.717511574076</v>
+        <v>46238.717499999999</v>
       </c>
       <c r="C189" s="3" t="s">
         <v>6</v>
@@ -5271,10 +5301,10 @@
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A190" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B190" s="2">
-        <v>46238.717511574076</v>
+        <v>46238.717499999999</v>
       </c>
       <c r="C190" s="3" t="s">
         <v>6</v>
@@ -5289,10 +5319,10 @@
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A191" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B191" s="2">
-        <v>46238.717523148145</v>
+        <v>46238.717511574076</v>
       </c>
       <c r="C191" s="3" t="s">
         <v>6</v>
@@ -5307,7 +5337,7 @@
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A192" s="1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B192" s="2">
         <v>46238.717511574076</v>
@@ -5325,7 +5355,7 @@
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A193" s="1" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B193" s="2">
         <v>46238.717523148145</v>
@@ -5343,7 +5373,7 @@
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A194" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B194" s="2">
         <v>46238.717511574076</v>
@@ -5361,7 +5391,7 @@
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A195" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B195" s="2">
         <v>46238.717523148145</v>
@@ -5379,10 +5409,10 @@
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A196" s="1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B196" s="2">
-        <v>46238.717523148145</v>
+        <v>46238.717511574076</v>
       </c>
       <c r="C196" s="3" t="s">
         <v>6</v>
@@ -5397,7 +5427,7 @@
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A197" s="1" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B197" s="2">
         <v>46238.717523148145</v>
@@ -5415,10 +5445,10 @@
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A198" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B198" s="2">
-        <v>46238.717534722222</v>
+        <v>46238.717523148145</v>
       </c>
       <c r="C198" s="3" t="s">
         <v>6</v>
@@ -5433,10 +5463,10 @@
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A199" s="1" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B199" s="2">
-        <v>46238.717546296299</v>
+        <v>46238.717523148145</v>
       </c>
       <c r="C199" s="3" t="s">
         <v>6</v>
@@ -5451,10 +5481,10 @@
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A200" s="1" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B200" s="2">
-        <v>46238.717546296299</v>
+        <v>46238.717534722222</v>
       </c>
       <c r="C200" s="3" t="s">
         <v>6</v>
@@ -5469,7 +5499,7 @@
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A201" s="1" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B201" s="2">
         <v>46238.717546296299</v>
@@ -5487,7 +5517,7 @@
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A202" s="1" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B202" s="2">
         <v>46238.717546296299</v>
@@ -5505,17 +5535,17 @@
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A203" s="1" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B203" s="2">
-        <v>46238.717152777775</v>
+        <v>46238.717546296299</v>
       </c>
       <c r="C203" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D203" s="4"/>
       <c r="E203" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F203" s="4" t="s">
         <v>27</v>
@@ -5523,10 +5553,10 @@
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A204" s="1" t="s">
-        <v>145</v>
+        <v>249</v>
       </c>
       <c r="B204" s="2">
-        <v>46238.717870370368</v>
+        <v>46238.717546296299</v>
       </c>
       <c r="C204" s="3" t="s">
         <v>6</v>
@@ -5536,33 +5566,33 @@
         <v>9</v>
       </c>
       <c r="F204" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A205" s="1" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="B205" s="2">
-        <v>46238.717557870368</v>
+        <v>46238.717152777775</v>
       </c>
       <c r="C205" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D205" s="4"/>
       <c r="E205" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F205" s="4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A206" s="1" t="s">
-        <v>249</v>
+        <v>148</v>
       </c>
       <c r="B206" s="2">
-        <v>46238.717569444445</v>
+        <v>46238.717870370368</v>
       </c>
       <c r="C206" s="3" t="s">
         <v>6</v>
@@ -5572,12 +5602,12 @@
         <v>9</v>
       </c>
       <c r="F206" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A207" s="1" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B207" s="2">
         <v>46238.717557870368</v>
@@ -5595,10 +5625,10 @@
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A208" s="1" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B208" s="2">
-        <v>46238.717557870368</v>
+        <v>46238.717569444445</v>
       </c>
       <c r="C208" s="3" t="s">
         <v>6</v>
@@ -5613,10 +5643,10 @@
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A209" s="1" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B209" s="2">
-        <v>46238.717569444445</v>
+        <v>46238.717557870368</v>
       </c>
       <c r="C209" s="3" t="s">
         <v>6</v>
@@ -5631,10 +5661,10 @@
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A210" s="1" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B210" s="2">
-        <v>46238.717569444445</v>
+        <v>46238.717557870368</v>
       </c>
       <c r="C210" s="3" t="s">
         <v>6</v>
@@ -5649,10 +5679,10 @@
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A211" s="1" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B211" s="2">
-        <v>46238.717650462961</v>
+        <v>46238.717569444445</v>
       </c>
       <c r="C211" s="3" t="s">
         <v>6</v>
@@ -5662,15 +5692,15 @@
         <v>9</v>
       </c>
       <c r="F211" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A212" s="1" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B212" s="2">
-        <v>46238.717650462961</v>
+        <v>46238.717569444445</v>
       </c>
       <c r="C212" s="3" t="s">
         <v>6</v>
@@ -5680,15 +5710,15 @@
         <v>9</v>
       </c>
       <c r="F212" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A213" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B213" s="2">
-        <v>46238.717638888891</v>
+        <v>46296.489074074074</v>
       </c>
       <c r="C213" s="3" t="s">
         <v>6</v>
@@ -5698,12 +5728,12 @@
         <v>9</v>
       </c>
       <c r="F213" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A214" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B214" s="2">
         <v>46238.717650462961</v>
@@ -5721,7 +5751,7 @@
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A215" s="1" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B215" s="2">
         <v>46238.717650462961</v>
@@ -5739,10 +5769,10 @@
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A216" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B216" s="2">
-        <v>46238.717650462961</v>
+        <v>46238.717638888891</v>
       </c>
       <c r="C216" s="3" t="s">
         <v>6</v>
@@ -5757,10 +5787,10 @@
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A217" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B217" s="2">
-        <v>46238.717662037037</v>
+        <v>46238.717650462961</v>
       </c>
       <c r="C217" s="3" t="s">
         <v>6</v>
@@ -5775,10 +5805,10 @@
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A218" s="1" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B218" s="2">
-        <v>46238.717557870368</v>
+        <v>46238.717650462961</v>
       </c>
       <c r="C218" s="3" t="s">
         <v>6</v>
@@ -5788,15 +5818,15 @@
         <v>9</v>
       </c>
       <c r="F218" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A219" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B219" s="2">
-        <v>46238.717546296299</v>
+        <v>46238.717650462961</v>
       </c>
       <c r="C219" s="3" t="s">
         <v>6</v>
@@ -5806,15 +5836,15 @@
         <v>9</v>
       </c>
       <c r="F219" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A220" s="1" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B220" s="2">
-        <v>46238.717546296299</v>
+        <v>46238.717662037037</v>
       </c>
       <c r="C220" s="3" t="s">
         <v>6</v>
@@ -5824,22 +5854,22 @@
         <v>9</v>
       </c>
       <c r="F220" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A221" s="1" t="s">
-        <v>210</v>
+        <v>265</v>
       </c>
       <c r="B221" s="2">
-        <v>46238.717152777775</v>
+        <v>46238.717557870368</v>
       </c>
       <c r="C221" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D221" s="4"/>
       <c r="E221" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F221" s="4" t="s">
         <v>31</v>
@@ -5847,10 +5877,10 @@
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A222" s="1" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B222" s="2">
-        <v>46238.717858796299</v>
+        <v>46238.717546296299</v>
       </c>
       <c r="C222" s="3" t="s">
         <v>6</v>
@@ -5860,51 +5890,51 @@
         <v>9</v>
       </c>
       <c r="F222" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A223" s="1" t="s">
-        <v>210</v>
+        <v>267</v>
       </c>
       <c r="B223" s="2">
-        <v>46238.717164351852</v>
+        <v>46238.717546296299</v>
       </c>
       <c r="C223" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D223" s="4"/>
       <c r="E223" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F223" s="4" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A224" s="1" t="s">
-        <v>265</v>
+        <v>213</v>
       </c>
       <c r="B224" s="2">
-        <v>46238.717870370368</v>
+        <v>46238.717152777775</v>
       </c>
       <c r="C224" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D224" s="4"/>
       <c r="E224" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F224" s="4" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A225" s="1" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B225" s="2">
-        <v>46238.717581018522</v>
+        <v>46238.717858796299</v>
       </c>
       <c r="C225" s="3" t="s">
         <v>6</v>
@@ -5914,12 +5944,12 @@
         <v>9</v>
       </c>
       <c r="F225" s="4" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A226" s="1" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="B226" s="2">
         <v>46238.717164351852</v>
@@ -5932,12 +5962,12 @@
         <v>8</v>
       </c>
       <c r="F226" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A227" s="1" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B227" s="2">
         <v>46238.717870370368</v>
@@ -5950,12 +5980,12 @@
         <v>9</v>
       </c>
       <c r="F227" s="4" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A228" s="1" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="B228" s="2">
         <v>46238.717581018522</v>
@@ -5968,33 +5998,33 @@
         <v>9</v>
       </c>
       <c r="F228" s="4" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A229" s="1" t="s">
-        <v>269</v>
+        <v>213</v>
       </c>
       <c r="B229" s="2">
-        <v>46238.717569444445</v>
+        <v>46238.717164351852</v>
       </c>
       <c r="C229" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D229" s="4"/>
       <c r="E229" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F229" s="4" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A230" s="1" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B230" s="2">
-        <v>46238.717569444445</v>
+        <v>46238.717870370368</v>
       </c>
       <c r="C230" s="3" t="s">
         <v>6</v>
@@ -6004,12 +6034,12 @@
         <v>9</v>
       </c>
       <c r="F230" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A231" s="1" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B231" s="2">
         <v>46238.717581018522</v>
@@ -6027,10 +6057,10 @@
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A232" s="1" t="s">
-        <v>259</v>
+        <v>273</v>
       </c>
       <c r="B232" s="2">
-        <v>46238.717581018522</v>
+        <v>46238.717569444445</v>
       </c>
       <c r="C232" s="3" t="s">
         <v>6</v>
@@ -6040,15 +6070,15 @@
         <v>9</v>
       </c>
       <c r="F232" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A233" s="1" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B233" s="2">
-        <v>46238.717581018522</v>
+        <v>46238.717569444445</v>
       </c>
       <c r="C233" s="3" t="s">
         <v>6</v>
@@ -6058,12 +6088,12 @@
         <v>9</v>
       </c>
       <c r="F233" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A234" s="1" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="B234" s="2">
         <v>46238.717581018522</v>
@@ -6076,12 +6106,12 @@
         <v>9</v>
       </c>
       <c r="F234" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="235" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A235" s="1" t="s">
-        <v>273</v>
+        <v>263</v>
       </c>
       <c r="B235" s="2">
         <v>46238.717581018522</v>
@@ -6099,10 +6129,10 @@
     </row>
     <row r="236" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A236" s="1" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="B236" s="2">
-        <v>46238.717592592591</v>
+        <v>46238.717581018522</v>
       </c>
       <c r="C236" s="3" t="s">
         <v>6</v>
@@ -6112,7 +6142,7 @@
         <v>9</v>
       </c>
       <c r="F236" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="237" spans="1:6" x14ac:dyDescent="0.3">
@@ -6120,7 +6150,7 @@
         <v>275</v>
       </c>
       <c r="B237" s="2">
-        <v>46238.717604166668</v>
+        <v>46238.717581018522</v>
       </c>
       <c r="C237" s="3" t="s">
         <v>6</v>
@@ -6130,15 +6160,15 @@
         <v>9</v>
       </c>
       <c r="F237" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="238" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A238" s="1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B238" s="2">
-        <v>46238.717604166668</v>
+        <v>46238.717581018522</v>
       </c>
       <c r="C238" s="3" t="s">
         <v>6</v>
@@ -6148,15 +6178,15 @@
         <v>9</v>
       </c>
       <c r="F238" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="239" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A239" s="1" t="s">
-        <v>277</v>
+        <v>257</v>
       </c>
       <c r="B239" s="2">
-        <v>46238.717604166668</v>
+        <v>46296.489074074074</v>
       </c>
       <c r="C239" s="3" t="s">
         <v>6</v>
@@ -6166,7 +6196,7 @@
         <v>9</v>
       </c>
       <c r="F239" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="240" spans="1:6" x14ac:dyDescent="0.3">
@@ -6174,7 +6204,7 @@
         <v>278</v>
       </c>
       <c r="B240" s="2">
-        <v>46238.717604166668</v>
+        <v>46238.717592592591</v>
       </c>
       <c r="C240" s="3" t="s">
         <v>6</v>
@@ -6210,7 +6240,7 @@
         <v>280</v>
       </c>
       <c r="B242" s="2">
-        <v>46238.717615740738</v>
+        <v>46238.717604166668</v>
       </c>
       <c r="C242" s="3" t="s">
         <v>6</v>
@@ -6228,7 +6258,7 @@
         <v>281</v>
       </c>
       <c r="B243" s="2">
-        <v>46238.717615740738</v>
+        <v>46238.717604166668</v>
       </c>
       <c r="C243" s="3" t="s">
         <v>6</v>
@@ -6246,7 +6276,7 @@
         <v>282</v>
       </c>
       <c r="B244" s="2">
-        <v>46238.717615740738</v>
+        <v>46238.717604166668</v>
       </c>
       <c r="C244" s="3" t="s">
         <v>6</v>
@@ -6264,7 +6294,7 @@
         <v>283</v>
       </c>
       <c r="B245" s="2">
-        <v>46238.717615740738</v>
+        <v>46238.717604166668</v>
       </c>
       <c r="C245" s="3" t="s">
         <v>6</v>
@@ -6282,7 +6312,7 @@
         <v>284</v>
       </c>
       <c r="B246" s="2">
-        <v>46238.717638888891</v>
+        <v>46238.717615740738</v>
       </c>
       <c r="C246" s="3" t="s">
         <v>6</v>
@@ -6300,7 +6330,7 @@
         <v>285</v>
       </c>
       <c r="B247" s="2">
-        <v>46238.717638888891</v>
+        <v>46238.717615740738</v>
       </c>
       <c r="C247" s="3" t="s">
         <v>6</v>
@@ -6318,7 +6348,7 @@
         <v>286</v>
       </c>
       <c r="B248" s="2">
-        <v>46238.717627314814</v>
+        <v>46238.717615740738</v>
       </c>
       <c r="C248" s="3" t="s">
         <v>6</v>
@@ -6336,7 +6366,7 @@
         <v>287</v>
       </c>
       <c r="B249" s="2">
-        <v>46238.717638888891</v>
+        <v>46238.717615740738</v>
       </c>
       <c r="C249" s="3" t="s">
         <v>6</v>
@@ -6354,7 +6384,7 @@
         <v>288</v>
       </c>
       <c r="B250" s="2">
-        <v>46238.717187499999</v>
+        <v>46238.717638888891</v>
       </c>
       <c r="C250" s="3" t="s">
         <v>6</v>
@@ -6364,7 +6394,7 @@
         <v>9</v>
       </c>
       <c r="F250" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="251" spans="1:6" x14ac:dyDescent="0.3">
@@ -6372,7 +6402,7 @@
         <v>289</v>
       </c>
       <c r="B251" s="2">
-        <v>46238.717187499999</v>
+        <v>46296.489074074074</v>
       </c>
       <c r="C251" s="3" t="s">
         <v>6</v>
@@ -6382,7 +6412,7 @@
         <v>9</v>
       </c>
       <c r="F251" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="252" spans="1:6" x14ac:dyDescent="0.3">
@@ -6390,7 +6420,7 @@
         <v>290</v>
       </c>
       <c r="B252" s="2">
-        <v>46238.717187499999</v>
+        <v>46296.489074074074</v>
       </c>
       <c r="C252" s="3" t="s">
         <v>6</v>
@@ -6400,7 +6430,7 @@
         <v>9</v>
       </c>
       <c r="F252" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.3">
@@ -6408,7 +6438,7 @@
         <v>291</v>
       </c>
       <c r="B253" s="2">
-        <v>46238.717222222222</v>
+        <v>46296.489085648151</v>
       </c>
       <c r="C253" s="3" t="s">
         <v>6</v>
@@ -6418,7 +6448,7 @@
         <v>9</v>
       </c>
       <c r="F253" s="4" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="254" spans="1:6" x14ac:dyDescent="0.3">
@@ -6426,7 +6456,7 @@
         <v>292</v>
       </c>
       <c r="B254" s="2">
-        <v>46238.717152777775</v>
+        <v>46296.489085648151</v>
       </c>
       <c r="C254" s="3" t="s">
         <v>6</v>
@@ -6436,7 +6466,7 @@
         <v>9</v>
       </c>
       <c r="F254" s="4" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="255" spans="1:6" x14ac:dyDescent="0.3">
@@ -6444,7 +6474,7 @@
         <v>293</v>
       </c>
       <c r="B255" s="2">
-        <v>46238.717233796298</v>
+        <v>46296.489085648151</v>
       </c>
       <c r="C255" s="3" t="s">
         <v>6</v>
@@ -6454,7 +6484,7 @@
         <v>9</v>
       </c>
       <c r="F255" s="4" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
     </row>
     <row r="256" spans="1:6" x14ac:dyDescent="0.3">
@@ -6462,7 +6492,7 @@
         <v>294</v>
       </c>
       <c r="B256" s="2">
-        <v>46238.717256944445</v>
+        <v>46238.717638888891</v>
       </c>
       <c r="C256" s="3" t="s">
         <v>6</v>
@@ -6472,7 +6502,7 @@
         <v>9</v>
       </c>
       <c r="F256" s="4" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
     </row>
     <row r="257" spans="1:6" x14ac:dyDescent="0.3">
@@ -6480,7 +6510,7 @@
         <v>295</v>
       </c>
       <c r="B257" s="2">
-        <v>46238.717199074075</v>
+        <v>46238.717627314814</v>
       </c>
       <c r="C257" s="3" t="s">
         <v>6</v>
@@ -6490,7 +6520,7 @@
         <v>9</v>
       </c>
       <c r="F257" s="4" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
     </row>
     <row r="258" spans="1:6" x14ac:dyDescent="0.3">
@@ -6498,7 +6528,7 @@
         <v>296</v>
       </c>
       <c r="B258" s="2">
-        <v>46238.717210648145</v>
+        <v>46238.717638888891</v>
       </c>
       <c r="C258" s="3" t="s">
         <v>6</v>
@@ -6508,7 +6538,7 @@
         <v>9</v>
       </c>
       <c r="F258" s="4" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
     </row>
     <row r="259" spans="1:6" x14ac:dyDescent="0.3">
@@ -6516,7 +6546,7 @@
         <v>297</v>
       </c>
       <c r="B259" s="2">
-        <v>46238.717210648145</v>
+        <v>46296.489085648151</v>
       </c>
       <c r="C259" s="3" t="s">
         <v>6</v>
@@ -6526,7 +6556,7 @@
         <v>9</v>
       </c>
       <c r="F259" s="4" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="260" spans="1:6" x14ac:dyDescent="0.3">
@@ -6534,7 +6564,7 @@
         <v>298</v>
       </c>
       <c r="B260" s="2">
-        <v>46238.717291666668</v>
+        <v>46296.489085648151</v>
       </c>
       <c r="C260" s="3" t="s">
         <v>6</v>
@@ -6544,7 +6574,7 @@
         <v>9</v>
       </c>
       <c r="F260" s="4" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
     </row>
     <row r="261" spans="1:6" x14ac:dyDescent="0.3">
@@ -6552,7 +6582,7 @@
         <v>299</v>
       </c>
       <c r="B261" s="2">
-        <v>46238.717291666668</v>
+        <v>46238.717187499999</v>
       </c>
       <c r="C261" s="3" t="s">
         <v>6</v>
@@ -6562,275 +6592,465 @@
         <v>9</v>
       </c>
       <c r="F261" s="4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="262" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A262" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="B262" s="2">
+        <v>46296.489108796297</v>
+      </c>
+      <c r="C262" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D262" s="4"/>
+      <c r="E262" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F262" s="4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="263" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A263" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="B263" s="2">
+        <v>46296.489108796297</v>
+      </c>
+      <c r="C263" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D263" s="4"/>
+      <c r="E263" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F263" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="264" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A264" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="B264" s="2">
+        <v>46296.489108796297</v>
+      </c>
+      <c r="C264" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D264" s="4"/>
+      <c r="E264" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F264" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="265" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A265" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="B265" s="2">
+        <v>46238.717233796298</v>
+      </c>
+      <c r="C265" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D265" s="4"/>
+      <c r="E265" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F265" s="4" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="266" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A266" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="B266" s="2">
+        <v>46238.717256944445</v>
+      </c>
+      <c r="C266" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D266" s="4"/>
+      <c r="E266" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F266" s="4" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="267" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A267" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="B267" s="2">
+        <v>46238.717199074075</v>
+      </c>
+      <c r="C267" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D267" s="4"/>
+      <c r="E267" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F267" s="4" t="s">
         <v>46</v>
+      </c>
+    </row>
+    <row r="268" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A268" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="B268" s="2">
+        <v>46238.717210648145</v>
+      </c>
+      <c r="C268" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D268" s="4"/>
+      <c r="E268" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F268" s="4" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="269" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A269" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="B269" s="2">
+        <v>46238.717210648145</v>
+      </c>
+      <c r="C269" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D269" s="4"/>
+      <c r="E269" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F269" s="4" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="270" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A270" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="B270" s="2">
+        <v>46238.717291666668</v>
+      </c>
+      <c r="C270" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D270" s="4"/>
+      <c r="E270" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F270" s="4" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="271" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A271" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="B271" s="2">
+        <v>46296.489108796297</v>
+      </c>
+      <c r="C271" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D271" s="4"/>
+      <c r="E271" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F271" s="4" t="s">
+        <v>47</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="A2" r:id="rId1" xr:uid="{3CD3AC5C-DBA0-4767-9FF9-3205E6FF7CA0}"/>
-    <hyperlink ref="A3" r:id="rId2" xr:uid="{3BC43B9E-03AD-44B7-8EBF-B1CE1C0BE220}"/>
-    <hyperlink ref="A4" r:id="rId3" xr:uid="{7975C5E7-608D-4CCE-9078-F8B35D51318A}"/>
-    <hyperlink ref="A5" r:id="rId4" xr:uid="{BC6089BF-0A3D-4AFD-ADB9-4B2E2065DEAC}"/>
-    <hyperlink ref="A6" r:id="rId5" xr:uid="{C5AA0AF4-A58F-4D55-A039-93E8447AD19E}"/>
-    <hyperlink ref="A7" r:id="rId6" xr:uid="{DE36C520-9B13-4C2D-81C9-152BB9D4EE3E}"/>
-    <hyperlink ref="A8" r:id="rId7" xr:uid="{7E199B96-11FC-41ED-905A-98B2152880F6}"/>
-    <hyperlink ref="A9" r:id="rId8" xr:uid="{4349F781-CC2E-4AE1-AC1A-63861027D9D3}"/>
-    <hyperlink ref="A10" r:id="rId9" xr:uid="{9A45167E-C911-4094-900D-B30A8C7BAC45}"/>
-    <hyperlink ref="A11" r:id="rId10" xr:uid="{5B1484D4-FEAD-4BCA-A0CE-F4A15618162A}"/>
-    <hyperlink ref="A12" r:id="rId11" xr:uid="{D855E1A6-742A-4497-9D9C-C93083D6D4B7}"/>
-    <hyperlink ref="A13" r:id="rId12" xr:uid="{F517380A-82CC-4930-8E26-0D2B10ABE15C}"/>
-    <hyperlink ref="A14" r:id="rId13" xr:uid="{4AC7BE9D-D434-4275-91B7-DF890826F50B}"/>
-    <hyperlink ref="A15" r:id="rId14" xr:uid="{8E1889D9-162C-4449-BEE3-6FC435ECE1EE}"/>
-    <hyperlink ref="A16" r:id="rId15" xr:uid="{3BEBF6A3-7F9E-4C7D-8EF7-E2202539199F}"/>
-    <hyperlink ref="A17" r:id="rId16" xr:uid="{939DF27B-403D-4635-B41F-531BC0C815FC}"/>
-    <hyperlink ref="A18" r:id="rId17" xr:uid="{DAE2131B-2DF1-47CA-AB16-D29EA58C0FA0}"/>
-    <hyperlink ref="A19" r:id="rId18" xr:uid="{DB6AAF4A-23BF-4C59-9AE8-70393FC3D81E}"/>
-    <hyperlink ref="A20" r:id="rId19" xr:uid="{B946656A-28AB-4B84-9110-647F6B2AD15A}"/>
-    <hyperlink ref="A21" r:id="rId20" xr:uid="{329729EC-501A-4E75-A7F8-A6ED70477CA8}"/>
-    <hyperlink ref="A22" r:id="rId21" xr:uid="{3B4FC4EE-047B-4D9E-85AC-68123A4582FB}"/>
-    <hyperlink ref="A23" r:id="rId22" xr:uid="{8DC90287-9644-4AD4-8E77-B962C45A6CF0}"/>
-    <hyperlink ref="A24" r:id="rId23" xr:uid="{F3F2CC4C-61D5-4541-8DC4-2BD441D64881}"/>
-    <hyperlink ref="A25" r:id="rId24" xr:uid="{2AF3A52F-6262-4EAF-AAD9-1FD63F115C53}"/>
-    <hyperlink ref="A26" r:id="rId25" xr:uid="{91D9BB3A-04AF-4032-ADF7-C1465ED6FEC0}"/>
-    <hyperlink ref="A27" r:id="rId26" xr:uid="{DE7AE9E8-CC8F-43C4-9B53-79D9B5CDC45B}"/>
-    <hyperlink ref="A28" r:id="rId27" xr:uid="{F51BB440-481A-4DAD-B732-02432D77A9C6}"/>
-    <hyperlink ref="A29" r:id="rId28" xr:uid="{D0234439-AFE0-4F74-AF45-379E7F360CF4}"/>
-    <hyperlink ref="A30" r:id="rId29" xr:uid="{7E23FB72-2497-423C-A2D2-3899069094B7}"/>
-    <hyperlink ref="A31" r:id="rId30" xr:uid="{FC3D3081-C4DF-4564-AF37-5C6F271B19E4}"/>
-    <hyperlink ref="A32" r:id="rId31" xr:uid="{B6C6C26E-4769-4ECE-8178-FAFE3220F474}"/>
-    <hyperlink ref="A33" r:id="rId32" xr:uid="{47434E40-2D7F-46BA-844D-777264146B64}"/>
-    <hyperlink ref="A34" r:id="rId33" xr:uid="{B7D16CC0-2891-4F13-8704-E7DA3098854C}"/>
-    <hyperlink ref="A35" r:id="rId34" xr:uid="{69BE2159-2C19-434F-9D37-5D951329BD2E}"/>
-    <hyperlink ref="A36" r:id="rId35" xr:uid="{B6DCC64B-E1BA-4C21-8F12-C0A9FAAE1ED1}"/>
-    <hyperlink ref="A37" r:id="rId36" xr:uid="{798A9872-DD42-4D04-B7B0-4F3897A4765E}"/>
-    <hyperlink ref="A38" r:id="rId37" xr:uid="{93EA3D5B-0508-4C0A-9C7B-C982BBC4DB87}"/>
-    <hyperlink ref="A39" r:id="rId38" xr:uid="{17432A73-A2A2-4E6C-8237-04A1DEAB938D}"/>
-    <hyperlink ref="A40" r:id="rId39" xr:uid="{27FB7B4A-B08F-4CEF-A755-828E6F861160}"/>
-    <hyperlink ref="A41" r:id="rId40" xr:uid="{C89CDB3E-397B-4532-95ED-D71C6F61F8E1}"/>
-    <hyperlink ref="A42" r:id="rId41" xr:uid="{CB9383C7-6D59-470B-9446-16F17723A407}"/>
-    <hyperlink ref="A43" r:id="rId42" xr:uid="{B0DD7443-236F-4C85-BA90-0E08FAEAAC0E}"/>
-    <hyperlink ref="A44" r:id="rId43" xr:uid="{619BCFCA-33C9-4B7B-B9EE-480410684F1D}"/>
-    <hyperlink ref="A45" r:id="rId44" xr:uid="{9A90D008-0D57-47E1-BFFB-6A30B13E4539}"/>
-    <hyperlink ref="A46" r:id="rId45" xr:uid="{BEF2D320-A333-489F-8DFA-2F9099A21E6C}"/>
-    <hyperlink ref="A47" r:id="rId46" xr:uid="{A09F20F7-698F-4D79-9AB5-6E7B684143A7}"/>
-    <hyperlink ref="A48" r:id="rId47" xr:uid="{543258AD-CE06-4AFF-A969-9F8557CFFE48}"/>
-    <hyperlink ref="A49" r:id="rId48" xr:uid="{FC694333-31CF-43AE-830F-105F8D4E6262}"/>
-    <hyperlink ref="A50" r:id="rId49" xr:uid="{1CE73CB9-D283-47F6-95DD-3A10FA11C830}"/>
-    <hyperlink ref="A51" r:id="rId50" xr:uid="{7F3A0BC0-6A76-4C1D-978B-6FC59F889805}"/>
-    <hyperlink ref="A52" r:id="rId51" xr:uid="{014DB348-F7E3-4464-9C1C-25F964F04CD0}"/>
-    <hyperlink ref="A53" r:id="rId52" xr:uid="{ED8879FF-3621-484A-8917-61A7F8455CC7}"/>
-    <hyperlink ref="A54" r:id="rId53" xr:uid="{916CA5B8-B0CD-494E-9AFB-9632D7E9AE6C}"/>
-    <hyperlink ref="A55" r:id="rId54" xr:uid="{0E442516-BECA-480F-88C4-05135D306C85}"/>
-    <hyperlink ref="A56" r:id="rId55" xr:uid="{4D71ABC9-6E42-49D0-8B84-EF53998CA8AC}"/>
-    <hyperlink ref="A57" r:id="rId56" xr:uid="{B480665E-2DC1-4BA2-AB4E-5284F950B92E}"/>
-    <hyperlink ref="A58" r:id="rId57" xr:uid="{45377739-5311-4810-AB91-1042824A8733}"/>
-    <hyperlink ref="A59" r:id="rId58" xr:uid="{1B966F94-4D73-47D9-BEFB-B7EAEE6D8F60}"/>
-    <hyperlink ref="A60" r:id="rId59" xr:uid="{5C583C8C-842C-4FD1-9563-62116CDC0CF1}"/>
-    <hyperlink ref="A61" r:id="rId60" xr:uid="{49409368-2EE3-492E-953C-58157BC3F4DA}"/>
-    <hyperlink ref="A62" r:id="rId61" xr:uid="{A7549F1E-92E3-48B7-B82F-4C8504632DA2}"/>
-    <hyperlink ref="A63" r:id="rId62" xr:uid="{90BCEB6E-67A3-40C9-A090-28257A8CCCFC}"/>
-    <hyperlink ref="A64" r:id="rId63" xr:uid="{FEFAA06C-AAE9-4BE6-9A38-347A90B470ED}"/>
-    <hyperlink ref="A65" r:id="rId64" xr:uid="{81CBDBFD-FEA5-4BB5-B7C9-BF9D54244D1D}"/>
-    <hyperlink ref="A66" r:id="rId65" xr:uid="{8456E18E-F17D-4C52-8301-A6E23B282215}"/>
-    <hyperlink ref="A67" r:id="rId66" xr:uid="{1B67BDAD-5276-41DC-903D-DE32C99A4D65}"/>
-    <hyperlink ref="A68" r:id="rId67" xr:uid="{D7B60C40-B508-4A7C-9AD6-723C44FFCFF1}"/>
-    <hyperlink ref="A69" r:id="rId68" xr:uid="{8F5DA027-E8EA-4A5F-AC16-838552DEC739}"/>
-    <hyperlink ref="A70" r:id="rId69" xr:uid="{3ADDC749-483F-4730-BB2A-9B92D4F2B4C5}"/>
-    <hyperlink ref="A71" r:id="rId70" xr:uid="{16F478E4-93FD-4D6F-A35B-91EE89EA09D3}"/>
-    <hyperlink ref="A72" r:id="rId71" xr:uid="{9C6DBB06-B226-4BE4-8776-AF56A44CD2D6}"/>
-    <hyperlink ref="A73" r:id="rId72" xr:uid="{7C0E14A8-B7A3-4ED6-85FD-29F9126357B3}"/>
-    <hyperlink ref="A74" r:id="rId73" xr:uid="{50709C56-4864-4714-810B-5AB3E4C614B7}"/>
-    <hyperlink ref="A75" r:id="rId74" xr:uid="{0992EE0D-C1A1-4698-B451-61A73CF0C4F0}"/>
-    <hyperlink ref="A76" r:id="rId75" xr:uid="{700E994F-B55C-4C27-83D6-9B9DBFC7584C}"/>
-    <hyperlink ref="A77" r:id="rId76" xr:uid="{B6EEC3C4-4EC9-4318-BBFB-9F3A1E86B93B}"/>
-    <hyperlink ref="A78" r:id="rId77" xr:uid="{2D714D52-0852-461F-B495-E15C0BB087C2}"/>
-    <hyperlink ref="A79" r:id="rId78" xr:uid="{218DF0BD-B5A8-43C8-987F-D9CC6917E400}"/>
-    <hyperlink ref="A80" r:id="rId79" xr:uid="{DA1980F6-BD84-4DFF-B7B4-3ED4D0AC70F7}"/>
-    <hyperlink ref="A81" r:id="rId80" xr:uid="{DFC36710-95C7-4F39-83D3-FC6E56D77EC0}"/>
-    <hyperlink ref="A82" r:id="rId81" xr:uid="{16EA9D27-E3EC-45BA-8AB8-DEC87E978A48}"/>
-    <hyperlink ref="A83" r:id="rId82" xr:uid="{B6213A54-AAAE-4964-876C-7FB0D426B009}"/>
-    <hyperlink ref="A84" r:id="rId83" xr:uid="{646121E7-520A-4D1F-B2BC-58F4BAFB7526}"/>
-    <hyperlink ref="A85" r:id="rId84" xr:uid="{DA80E0D7-DDBA-4F35-B84C-6C3C21AEE206}"/>
-    <hyperlink ref="A86" r:id="rId85" xr:uid="{93C4EE0B-4593-4DEB-8C1F-F2FA1149FAAE}"/>
-    <hyperlink ref="A87" r:id="rId86" xr:uid="{ABEC42BA-9F73-4C70-B520-D95C0B124B41}"/>
-    <hyperlink ref="A88" r:id="rId87" xr:uid="{D545C80D-BF65-49B6-A105-029F6EF0E307}"/>
-    <hyperlink ref="A89" r:id="rId88" xr:uid="{CA48C68D-FB31-4E81-8936-41111993A1E2}"/>
-    <hyperlink ref="A90" r:id="rId89" xr:uid="{3F9C8BD4-63FD-4D0B-B621-CB4D2E8B8546}"/>
-    <hyperlink ref="A91" r:id="rId90" xr:uid="{E66F4ADC-2098-4622-879D-465105FA2C04}"/>
-    <hyperlink ref="A92" r:id="rId91" xr:uid="{34D61FF6-6B98-4203-91D6-64E4CF7B58A9}"/>
-    <hyperlink ref="A93" r:id="rId92" xr:uid="{9ED209B9-5B0D-470C-AFCD-62AF41E28753}"/>
-    <hyperlink ref="A94" r:id="rId93" xr:uid="{26358B53-259D-48F2-956C-702639E4F66F}"/>
-    <hyperlink ref="A95" r:id="rId94" xr:uid="{471FA8A3-3BD5-4448-9B49-1DD4A335DB25}"/>
-    <hyperlink ref="A96" r:id="rId95" xr:uid="{03968410-68A6-4014-B3B3-091E314E2988}"/>
-    <hyperlink ref="A97" r:id="rId96" xr:uid="{7A9FCEE2-45FE-474B-B848-262CA120C30D}"/>
-    <hyperlink ref="A98" r:id="rId97" xr:uid="{DD104809-4A5B-45AF-8758-1597C7B74ABA}"/>
-    <hyperlink ref="A99" r:id="rId98" xr:uid="{B6DEDAF2-3D32-4506-98D3-D3210CC7B386}"/>
-    <hyperlink ref="A100" r:id="rId99" xr:uid="{96755034-25A8-4B55-A029-9BFF8062B07E}"/>
-    <hyperlink ref="A101" r:id="rId100" xr:uid="{DF230D38-0BA5-403B-B158-794D17E53C59}"/>
-    <hyperlink ref="A102" r:id="rId101" xr:uid="{A9BC6D7F-418E-45DB-9FC7-B889A37B56AB}"/>
-    <hyperlink ref="A103" r:id="rId102" xr:uid="{733D121D-90CE-46F0-9F80-F68B3190F16A}"/>
-    <hyperlink ref="A104" r:id="rId103" xr:uid="{94ADD00D-90EF-4EC5-89A9-2AB4791EED71}"/>
-    <hyperlink ref="A105" r:id="rId104" xr:uid="{A8764186-E6DB-47DE-9E33-37D1A8E005A1}"/>
-    <hyperlink ref="A106" r:id="rId105" xr:uid="{DB6C8BE4-865B-48D2-8F65-ED5E494825CD}"/>
-    <hyperlink ref="A107" r:id="rId106" xr:uid="{922CB6E2-52C0-4FF0-B655-9EF412546445}"/>
-    <hyperlink ref="A108" r:id="rId107" xr:uid="{87F2139B-95EF-41D7-8274-56C5F0ACE4FD}"/>
-    <hyperlink ref="A109" r:id="rId108" xr:uid="{527D87DE-92C6-4954-B196-C68273E42214}"/>
-    <hyperlink ref="A110" r:id="rId109" xr:uid="{7A679E42-9D06-4A55-8940-E8886851AD82}"/>
-    <hyperlink ref="A111" r:id="rId110" xr:uid="{61F35E1F-C795-4462-AA68-E79EAB3862CC}"/>
-    <hyperlink ref="A112" r:id="rId111" xr:uid="{D0984735-DCB3-4BB1-B438-854939359EFC}"/>
-    <hyperlink ref="A113" r:id="rId112" xr:uid="{33C572D3-BDCE-4EC7-8460-4D733C58AABB}"/>
-    <hyperlink ref="A114" r:id="rId113" xr:uid="{5BD59ACE-1CC4-4980-A4B5-2FF8FE22CD3B}"/>
-    <hyperlink ref="A115" r:id="rId114" xr:uid="{25EDFBDE-73C5-4997-A36C-C3C9F39C63F1}"/>
-    <hyperlink ref="A116" r:id="rId115" xr:uid="{3C2DBFA3-8EF2-4ED4-9110-9168C7986274}"/>
-    <hyperlink ref="A117" r:id="rId116" xr:uid="{A3A5279C-15BC-4960-9FC8-6B149BCFF26C}"/>
-    <hyperlink ref="A118" r:id="rId117" xr:uid="{22E57DFF-A6F3-4F5B-A56C-AD5CCBC22EB8}"/>
-    <hyperlink ref="A119" r:id="rId118" xr:uid="{530D3526-AAB4-47D6-9539-0B4DC8C8AC8B}"/>
-    <hyperlink ref="A120" r:id="rId119" xr:uid="{6E5937D0-E7F1-4A25-9520-AC7996F1A3DA}"/>
-    <hyperlink ref="A121" r:id="rId120" xr:uid="{F11CC14D-0CA9-4576-86C1-B2EE52CEF5BD}"/>
-    <hyperlink ref="A122" r:id="rId121" xr:uid="{74F58606-A58C-4CEC-84BA-A0D8C7A3B9E3}"/>
-    <hyperlink ref="A123" r:id="rId122" xr:uid="{8E554AB8-B7AB-42DE-A39F-88A1AB70CB8D}"/>
-    <hyperlink ref="A124" r:id="rId123" xr:uid="{EDE23DD2-184F-490E-9310-777C539FC468}"/>
-    <hyperlink ref="A125" r:id="rId124" xr:uid="{F4D0A91E-07B4-48FE-80CD-4F6CCE1AE54A}"/>
-    <hyperlink ref="A126" r:id="rId125" xr:uid="{7055DF0D-DB44-46D5-A815-E6209387DA47}"/>
-    <hyperlink ref="A127" r:id="rId126" xr:uid="{300F88E9-D392-4CE0-953E-C937E9041425}"/>
-    <hyperlink ref="A128" r:id="rId127" xr:uid="{AD8BC20D-0B9D-4A90-8188-1819F616F2DC}"/>
-    <hyperlink ref="A129" r:id="rId128" xr:uid="{E78EDFEF-8DE6-4814-9682-701E91706C16}"/>
-    <hyperlink ref="A130" r:id="rId129" xr:uid="{293A0CAE-6F1A-47CA-8DBC-ED980FB269F0}"/>
-    <hyperlink ref="A131" r:id="rId130" xr:uid="{93F99AF3-04E8-42BD-BB42-DD45BE6B4226}"/>
-    <hyperlink ref="A132" r:id="rId131" xr:uid="{CB73541B-98A7-462A-8CC7-932B5861B3BE}"/>
-    <hyperlink ref="A133" r:id="rId132" xr:uid="{8AC57A9B-0504-47F8-BC37-2E4A53D18498}"/>
-    <hyperlink ref="A134" r:id="rId133" xr:uid="{271A76CB-975D-441E-A82C-CC7175E113AD}"/>
-    <hyperlink ref="A135" r:id="rId134" xr:uid="{AAD18AD2-7A12-4C95-A494-AF2E7BE973B8}"/>
-    <hyperlink ref="A136" r:id="rId135" xr:uid="{CC232F17-DC67-4A7B-B99B-F99A4090DBCB}"/>
-    <hyperlink ref="A137" r:id="rId136" xr:uid="{A428E03F-6EB4-4FEC-9B1B-4910E3817DFB}"/>
-    <hyperlink ref="A138" r:id="rId137" xr:uid="{4D15DE20-06BC-471A-A46C-056C634C888D}"/>
-    <hyperlink ref="A139" r:id="rId138" xr:uid="{7E8BAB18-8FEC-4F6D-ABF8-2F45F0D2C05D}"/>
-    <hyperlink ref="A140" r:id="rId139" xr:uid="{ED0D0EF1-8A59-49AB-A24B-9B3CB58855B0}"/>
-    <hyperlink ref="A141" r:id="rId140" xr:uid="{930B312F-AC89-40D2-B057-18BF70C6115C}"/>
-    <hyperlink ref="A142" r:id="rId141" xr:uid="{89F3AA4E-3F36-4DE7-980B-B7F83D9A861E}"/>
-    <hyperlink ref="A143" r:id="rId142" xr:uid="{738110DD-AB70-4DC2-B82A-19B34AE6BCD0}"/>
-    <hyperlink ref="A144" r:id="rId143" xr:uid="{BDD77E33-F6B6-4A04-9AD3-40BDEEC24565}"/>
-    <hyperlink ref="A145" r:id="rId144" xr:uid="{F711913B-24E9-4C7D-A6D1-FC24929CD324}"/>
-    <hyperlink ref="A146" r:id="rId145" xr:uid="{B3388EF6-E73D-463F-92F3-054711BD7C0C}"/>
-    <hyperlink ref="A147" r:id="rId146" xr:uid="{15F84656-9879-4E7F-B96E-CA3972057C64}"/>
-    <hyperlink ref="A148" r:id="rId147" xr:uid="{FF56AE72-B184-4D0B-B854-E58C27DF5EF4}"/>
-    <hyperlink ref="A149" r:id="rId148" xr:uid="{0E45E6C1-9EA0-4120-8EDC-FEB437193837}"/>
-    <hyperlink ref="A150" r:id="rId149" xr:uid="{3A24722F-F4E7-472C-92BB-9E53CF504BF4}"/>
-    <hyperlink ref="A151" r:id="rId150" xr:uid="{61A62963-F815-4DB4-9D38-F61E84FC41C3}"/>
-    <hyperlink ref="A152" r:id="rId151" xr:uid="{C06E9224-C98A-431B-AA85-2FA84B3AC4A5}"/>
-    <hyperlink ref="A153" r:id="rId152" xr:uid="{6557CAD0-88AD-4AC3-ABD8-81EB4E596F02}"/>
-    <hyperlink ref="A154" r:id="rId153" xr:uid="{0F4B427D-DC69-48C1-BD99-5ECBCE95DDDA}"/>
-    <hyperlink ref="A155" r:id="rId154" xr:uid="{9F92E6A7-DC7D-47DB-AD24-7802C9C702E3}"/>
-    <hyperlink ref="A156" r:id="rId155" xr:uid="{9AA8DBFD-3A63-4306-88FD-020402BACE3F}"/>
-    <hyperlink ref="A157" r:id="rId156" xr:uid="{14B72A85-D9F0-4D93-B451-D10AC53F302C}"/>
-    <hyperlink ref="A158" r:id="rId157" xr:uid="{E6750508-B6C5-4E2E-8F02-6A2B5D679BEC}"/>
-    <hyperlink ref="A159" r:id="rId158" xr:uid="{5A9D1EF3-BA5A-4370-811A-6B1532ADA0E5}"/>
-    <hyperlink ref="A160" r:id="rId159" xr:uid="{2E705E54-4034-4BC4-871E-04F947A9D1A3}"/>
-    <hyperlink ref="A161" r:id="rId160" xr:uid="{E1E3D5A3-29F9-4FC2-B4F1-592044552DB8}"/>
-    <hyperlink ref="A162" r:id="rId161" xr:uid="{FFDE9772-650B-4CF6-9821-91C2922E5A2C}"/>
-    <hyperlink ref="A163" r:id="rId162" xr:uid="{9702BFA8-EE39-46A5-B481-E1AC23C519E4}"/>
-    <hyperlink ref="A164" r:id="rId163" xr:uid="{2467A108-1B1A-439F-A382-0749C23DE111}"/>
-    <hyperlink ref="A165" r:id="rId164" xr:uid="{93AB96C3-15CC-4676-A872-D495B9C9CA9D}"/>
-    <hyperlink ref="A166" r:id="rId165" xr:uid="{B8AC24C1-B08A-49C5-BBC0-B84A8408B2FE}"/>
-    <hyperlink ref="A167" r:id="rId166" xr:uid="{0DC25CF0-523A-45A3-B1CB-EA392CC2B0CF}"/>
-    <hyperlink ref="A168" r:id="rId167" xr:uid="{0CE464B4-14C0-4844-889D-26542925BD7A}"/>
-    <hyperlink ref="A169" r:id="rId168" xr:uid="{E4104115-C0F3-4733-A1A6-084F30C33AE3}"/>
-    <hyperlink ref="A170" r:id="rId169" xr:uid="{8DD790B4-DA15-4E18-8C13-74AAD5A79F32}"/>
-    <hyperlink ref="A171" r:id="rId170" xr:uid="{6F75C449-CF98-466F-BD68-74676D92FBB4}"/>
-    <hyperlink ref="A172" r:id="rId171" xr:uid="{847BF445-3A57-49BA-B2D2-7B29878339A6}"/>
-    <hyperlink ref="A173" r:id="rId172" xr:uid="{E0B732C3-7B14-4CF8-B9FD-AA3B62F1F8C5}"/>
-    <hyperlink ref="A174" r:id="rId173" xr:uid="{48D3AB95-C005-4AB1-A56B-283F7CB98D7B}"/>
-    <hyperlink ref="A175" r:id="rId174" xr:uid="{7675F8D4-E7DB-414C-B198-CF4C0BCA601C}"/>
-    <hyperlink ref="A176" r:id="rId175" xr:uid="{5793BAEC-3031-4787-BBC7-085AD3317772}"/>
-    <hyperlink ref="A177" r:id="rId176" xr:uid="{08A64D36-CD37-4909-96DC-DD89BA8CBF2E}"/>
-    <hyperlink ref="A178" r:id="rId177" xr:uid="{90BA5489-CD5B-451A-93C9-21199CCEE9AF}"/>
-    <hyperlink ref="A179" r:id="rId178" xr:uid="{185BBE90-5B84-4519-BAC4-198C1294FC1C}"/>
-    <hyperlink ref="A180" r:id="rId179" xr:uid="{F598FCAF-BA88-4AC9-B3CE-01C1FB07E06A}"/>
-    <hyperlink ref="A181" r:id="rId180" xr:uid="{4C85A5CD-A4E7-4892-B202-6494F64AFDB6}"/>
-    <hyperlink ref="A182" r:id="rId181" xr:uid="{69C5F917-95DA-4DF3-8152-C532FAF9CEB3}"/>
-    <hyperlink ref="A183" r:id="rId182" xr:uid="{3C779285-F62F-43EB-8E61-2C4E1D2A7716}"/>
-    <hyperlink ref="A184" r:id="rId183" xr:uid="{6360F757-923A-46F2-BE9D-8287A6572018}"/>
-    <hyperlink ref="A185" r:id="rId184" xr:uid="{8C9EE01A-714D-4E2D-9DA2-4EF370EF0DEE}"/>
-    <hyperlink ref="A186" r:id="rId185" xr:uid="{036758F8-E01A-4F02-96E1-22D743A0CC5C}"/>
-    <hyperlink ref="A187" r:id="rId186" xr:uid="{FD727543-B895-4E98-BA1F-DBCAE63E42B5}"/>
-    <hyperlink ref="A188" r:id="rId187" xr:uid="{BBE10196-8098-4F6C-9613-E50A142D73B4}"/>
-    <hyperlink ref="A189" r:id="rId188" xr:uid="{37ED037E-8921-43E7-8B96-8EC106E0219B}"/>
-    <hyperlink ref="A190" r:id="rId189" xr:uid="{B60ED5E1-50DC-4979-B2D2-3743242E959C}"/>
-    <hyperlink ref="A191" r:id="rId190" xr:uid="{EDC8C059-8686-4890-8661-3BC2120EB38A}"/>
-    <hyperlink ref="A192" r:id="rId191" xr:uid="{386070A9-9461-40A6-B548-8931A5B1BBAB}"/>
-    <hyperlink ref="A193" r:id="rId192" xr:uid="{1B4F71E4-F310-4CB1-9923-386753990976}"/>
-    <hyperlink ref="A194" r:id="rId193" xr:uid="{1EB86B59-412A-4E4B-8369-4BE7E3D786EA}"/>
-    <hyperlink ref="A195" r:id="rId194" xr:uid="{564020B0-0E1E-4FEF-A59E-3A60F3351DE1}"/>
-    <hyperlink ref="A196" r:id="rId195" xr:uid="{0EC30150-1C9B-4B29-9D07-74F33948A2E2}"/>
-    <hyperlink ref="A197" r:id="rId196" xr:uid="{C6A3D443-9C13-47CA-B8C4-644490F25C40}"/>
-    <hyperlink ref="A198" r:id="rId197" xr:uid="{9D691D03-7A57-4A6C-A838-444EA8B4C5AF}"/>
-    <hyperlink ref="A199" r:id="rId198" xr:uid="{83D6D80E-9A53-417D-A381-9250E656150C}"/>
-    <hyperlink ref="A200" r:id="rId199" xr:uid="{A1862B13-0A92-4661-B25A-987DD62F5117}"/>
-    <hyperlink ref="A201" r:id="rId200" xr:uid="{DCAAE0B1-4C71-4B11-A91C-D83F2E22ED47}"/>
-    <hyperlink ref="A202" r:id="rId201" xr:uid="{1C049A4A-24B3-4C78-B900-96C21EE1E2DE}"/>
-    <hyperlink ref="A203" r:id="rId202" xr:uid="{F0D17D4C-B95F-4439-83E7-5BD52F755091}"/>
-    <hyperlink ref="A204" r:id="rId203" xr:uid="{4886E8CC-8C0D-43E0-8FA5-8E4450951C75}"/>
-    <hyperlink ref="A205" r:id="rId204" xr:uid="{BCAEB9AA-1238-486F-A99D-09B9430EF568}"/>
-    <hyperlink ref="A206" r:id="rId205" xr:uid="{A4EDA14A-6EB0-47A6-BA7A-69A91307818B}"/>
-    <hyperlink ref="A207" r:id="rId206" xr:uid="{FABFBFE5-3E5C-4F19-A8FB-498584CD024B}"/>
-    <hyperlink ref="A208" r:id="rId207" xr:uid="{E2AD6AB8-7DB5-48D9-998C-4EE65E04B84C}"/>
-    <hyperlink ref="A209" r:id="rId208" xr:uid="{048B4B11-C798-45D7-A103-68DC124DBD6D}"/>
-    <hyperlink ref="A210" r:id="rId209" xr:uid="{45F3C3A5-FCD8-48CE-8F3E-76BD37E193FB}"/>
-    <hyperlink ref="A211" r:id="rId210" xr:uid="{B06DBD94-DF1F-48E6-BC3F-5F15B6FD60A1}"/>
-    <hyperlink ref="A212" r:id="rId211" xr:uid="{71B9AAC3-BD97-4718-ACF1-9138563C837E}"/>
-    <hyperlink ref="A213" r:id="rId212" xr:uid="{EB8ACE35-435A-4E3D-87F2-2ABA346C2D07}"/>
-    <hyperlink ref="A214" r:id="rId213" xr:uid="{95B2B96D-291F-40D7-A027-2ECE4B5D6789}"/>
-    <hyperlink ref="A215" r:id="rId214" xr:uid="{74C1C147-714F-4EC6-A55E-FB876D59BEB5}"/>
-    <hyperlink ref="A216" r:id="rId215" xr:uid="{1561CC6B-DDDD-4508-9324-F290E9C694B6}"/>
-    <hyperlink ref="A217" r:id="rId216" xr:uid="{772F0832-E9DE-465C-8B1B-EFA34A95BF06}"/>
-    <hyperlink ref="A218" r:id="rId217" xr:uid="{9E38AA04-DABE-4CFE-82C5-9FF847562DDC}"/>
-    <hyperlink ref="A219" r:id="rId218" xr:uid="{02FA5D3A-F000-4F4A-ABD6-CF5B90B94E42}"/>
-    <hyperlink ref="A220" r:id="rId219" xr:uid="{C03F376F-3741-412D-A93A-C64A43EE5A17}"/>
-    <hyperlink ref="A221" r:id="rId220" xr:uid="{9471BB78-773E-4DC4-89B6-D41DC1AEE65C}"/>
-    <hyperlink ref="A222" r:id="rId221" xr:uid="{AE1AA106-D61E-4D9A-871A-EB300C9DBB78}"/>
-    <hyperlink ref="A223" r:id="rId222" xr:uid="{C1F26A4C-D1EC-41B4-B3F8-B24B42593EA2}"/>
-    <hyperlink ref="A224" r:id="rId223" xr:uid="{2F8244D8-0709-4549-9173-0C7994DA2FB2}"/>
-    <hyperlink ref="A225" r:id="rId224" xr:uid="{844FD26D-F5F7-4365-A120-80259464E82E}"/>
-    <hyperlink ref="A226" r:id="rId225" xr:uid="{FDB75819-BCFE-474F-9109-3BB3441C18E5}"/>
-    <hyperlink ref="A227" r:id="rId226" xr:uid="{E7C62A22-8E4A-4D5D-B7C8-053626AEF39B}"/>
-    <hyperlink ref="A228" r:id="rId227" xr:uid="{83C174F9-4A36-4CAD-A352-F4CD4F7082D4}"/>
-    <hyperlink ref="A229" r:id="rId228" xr:uid="{5E6D1875-D16C-4A56-A7D6-1B336DFEA762}"/>
-    <hyperlink ref="A230" r:id="rId229" xr:uid="{267D22C2-DC12-4B7D-8CA1-9DB8A5D754DB}"/>
-    <hyperlink ref="A231" r:id="rId230" xr:uid="{BD316408-ABD7-4F77-9BDE-0220D5A7F449}"/>
-    <hyperlink ref="A232" r:id="rId231" xr:uid="{6DF5C937-C935-40CC-AAF5-125743AB634F}"/>
-    <hyperlink ref="A233" r:id="rId232" xr:uid="{7719A5B8-92C1-4008-AC45-33230E1117A2}"/>
-    <hyperlink ref="A234" r:id="rId233" xr:uid="{AAFB749D-8892-4DCC-95F8-993FA7218773}"/>
-    <hyperlink ref="A235" r:id="rId234" xr:uid="{C9CF4146-AABC-47F4-91E8-157D3F8BA856}"/>
-    <hyperlink ref="A236" r:id="rId235" xr:uid="{2E63FD76-ED81-4CCB-99DB-B015A4E3B5C6}"/>
-    <hyperlink ref="A237" r:id="rId236" xr:uid="{6CAADA68-B5A3-4E62-8315-0132F5ABE25A}"/>
-    <hyperlink ref="A238" r:id="rId237" xr:uid="{20020261-37B6-4342-898B-AD300A2DFF42}"/>
-    <hyperlink ref="A239" r:id="rId238" xr:uid="{EBA8CE24-D4AD-4422-A559-56CCD150AFC9}"/>
-    <hyperlink ref="A240" r:id="rId239" xr:uid="{92BC8956-568A-451E-A3D5-F37B77F00B06}"/>
-    <hyperlink ref="A241" r:id="rId240" xr:uid="{04D0C1B0-CE8E-4A78-BF3B-2532F7210387}"/>
-    <hyperlink ref="A242" r:id="rId241" xr:uid="{0880D7F2-03C0-411E-BF52-0D3B4AA0C113}"/>
-    <hyperlink ref="A243" r:id="rId242" xr:uid="{1C418A2D-285F-412E-9A4B-8441533E28D6}"/>
-    <hyperlink ref="A244" r:id="rId243" xr:uid="{17E66E97-7A7E-44B5-8A5F-9DCEBA9AC4D5}"/>
-    <hyperlink ref="A245" r:id="rId244" xr:uid="{B8ABE170-6B8C-4D7A-AAEA-D3097C02167D}"/>
-    <hyperlink ref="A246" r:id="rId245" xr:uid="{B38D0C93-FCFC-4B27-AB5D-A774631BDB70}"/>
-    <hyperlink ref="A247" r:id="rId246" xr:uid="{A2D81A4A-D927-4A3A-A069-CCD3CFBDDA4E}"/>
-    <hyperlink ref="A248" r:id="rId247" xr:uid="{53EDE1D2-0848-4E65-B574-6F6CF5767482}"/>
-    <hyperlink ref="A249" r:id="rId248" xr:uid="{BE8B07BF-49CF-492F-9CF2-02BECC85344E}"/>
-    <hyperlink ref="A250" r:id="rId249" xr:uid="{D1316402-2D4A-4C67-9C8B-74BFC6CACEEC}"/>
-    <hyperlink ref="A251" r:id="rId250" xr:uid="{EA340EA5-BFC1-4300-BFAA-2A963295C882}"/>
-    <hyperlink ref="A252" r:id="rId251" xr:uid="{EB7ADCDC-565B-4A83-8A06-16962752A6BB}"/>
-    <hyperlink ref="A253" r:id="rId252" xr:uid="{60504F6D-D4C6-4095-98EF-F0AD8C86C42C}"/>
-    <hyperlink ref="A254" r:id="rId253" xr:uid="{BD36CB8E-C015-4B5C-80FC-19DA7A659B36}"/>
-    <hyperlink ref="A255" r:id="rId254" xr:uid="{09163866-9D3F-45E5-848B-D9B71E78A673}"/>
-    <hyperlink ref="A256" r:id="rId255" xr:uid="{15D0192B-B1AD-410D-B651-CC6ED29A2AE8}"/>
-    <hyperlink ref="A257" r:id="rId256" xr:uid="{F919D205-DCE3-41AD-BF5B-39914207F9F9}"/>
-    <hyperlink ref="A258" r:id="rId257" xr:uid="{F8F78A7D-A69C-4BCD-80FB-DE0A8E8D6836}"/>
-    <hyperlink ref="A259" r:id="rId258" xr:uid="{DE8D4325-77F6-41BE-9233-831AF5AD689F}"/>
-    <hyperlink ref="A260" r:id="rId259" xr:uid="{3E2C0BCE-56E7-4F95-A881-E7CB2355019D}"/>
-    <hyperlink ref="A261" r:id="rId260" xr:uid="{7765ED36-BD1B-4157-B480-5890A3D32A10}"/>
+    <hyperlink ref="A2" r:id="rId1" xr:uid="{638BF431-AB51-4526-BCDA-366ED70AE0D7}"/>
+    <hyperlink ref="A3" r:id="rId2" xr:uid="{029BF007-AA3A-4309-9443-6937283E9736}"/>
+    <hyperlink ref="A4" r:id="rId3" xr:uid="{FA90869D-E9E3-4983-BA93-167CB0DC5BCA}"/>
+    <hyperlink ref="A5" r:id="rId4" xr:uid="{CAE39E93-9A11-43CA-9B26-1E8B2300134D}"/>
+    <hyperlink ref="A6" r:id="rId5" xr:uid="{9DE5F9D4-2856-448A-9224-C59ED56FF68F}"/>
+    <hyperlink ref="A7" r:id="rId6" xr:uid="{5B14D651-5BFC-4094-B57C-DC095FDA41DB}"/>
+    <hyperlink ref="A8" r:id="rId7" xr:uid="{8BD2201E-31C7-4A1C-B575-C4F4574BEF83}"/>
+    <hyperlink ref="A9" r:id="rId8" xr:uid="{681200E6-A2AB-45FF-9662-DB2F9B2846E9}"/>
+    <hyperlink ref="A10" r:id="rId9" xr:uid="{DC7C1B20-2F75-4E0C-8A75-71839E5E4FFA}"/>
+    <hyperlink ref="A11" r:id="rId10" xr:uid="{D6DD3E84-B23F-4349-8875-D7378B566DB0}"/>
+    <hyperlink ref="A12" r:id="rId11" xr:uid="{AC3E11ED-0C03-4934-88C3-85786E4B5014}"/>
+    <hyperlink ref="A13" r:id="rId12" xr:uid="{D196A956-1F06-4D6C-98DD-92B2842D2B04}"/>
+    <hyperlink ref="A14" r:id="rId13" xr:uid="{8E735968-46EF-49B1-97D3-D434E0935FC5}"/>
+    <hyperlink ref="A15" r:id="rId14" xr:uid="{04B7717C-04F2-4A96-B5AD-ED9847059F8C}"/>
+    <hyperlink ref="A16" r:id="rId15" xr:uid="{E6CBF10A-16EF-48C0-BEFE-393F40DC1EC5}"/>
+    <hyperlink ref="A17" r:id="rId16" xr:uid="{8541983F-6282-42AF-ABEE-1ED9DC10A57A}"/>
+    <hyperlink ref="A18" r:id="rId17" xr:uid="{5FFDF0B3-D146-4045-A74B-4022A07EB5C9}"/>
+    <hyperlink ref="A19" r:id="rId18" xr:uid="{53BC2F25-CECB-41C7-9DDB-CC5EC81BFC0F}"/>
+    <hyperlink ref="A20" r:id="rId19" xr:uid="{AAD9B4A2-A6A7-435D-B39F-32F0FFC098D9}"/>
+    <hyperlink ref="A21" r:id="rId20" xr:uid="{245EDB43-A36F-4775-A2FB-B4422B004407}"/>
+    <hyperlink ref="A22" r:id="rId21" xr:uid="{8A40EE5F-F50B-4002-9FAC-A70B607E7680}"/>
+    <hyperlink ref="A23" r:id="rId22" xr:uid="{11A35F3F-96F7-4F44-8B9E-5FAAD3B26165}"/>
+    <hyperlink ref="A24" r:id="rId23" xr:uid="{3FB1FCE7-7E21-49F3-9BB9-0F575966209C}"/>
+    <hyperlink ref="A25" r:id="rId24" xr:uid="{23C7B90B-DBCA-4D76-B9D4-FAF1EEF42332}"/>
+    <hyperlink ref="A26" r:id="rId25" xr:uid="{50F5F957-69DA-4420-A64D-A48B6989EC24}"/>
+    <hyperlink ref="A27" r:id="rId26" xr:uid="{F6312842-2E96-4A7E-8A66-9A0E70BA6E58}"/>
+    <hyperlink ref="A28" r:id="rId27" xr:uid="{EE6ACB29-BEE6-4581-AE9C-8D7D331C0F75}"/>
+    <hyperlink ref="A29" r:id="rId28" xr:uid="{7AF4EB2A-1F5C-46AA-983F-B52320564090}"/>
+    <hyperlink ref="A30" r:id="rId29" xr:uid="{508B3B99-AD65-4814-9836-EB9C23EAB96F}"/>
+    <hyperlink ref="A31" r:id="rId30" xr:uid="{DE87E9D8-3C9D-49E8-985F-1E1BA99F84DE}"/>
+    <hyperlink ref="A32" r:id="rId31" xr:uid="{7BBF45F2-27BA-41BC-A00B-5246BD752F9F}"/>
+    <hyperlink ref="A33" r:id="rId32" xr:uid="{293369AF-A3CD-4FAC-AC8C-E93ED6FCC486}"/>
+    <hyperlink ref="A34" r:id="rId33" xr:uid="{F72ED837-4A38-4E71-9C08-3F2A0F2CAEE7}"/>
+    <hyperlink ref="A35" r:id="rId34" xr:uid="{6858BB77-D15F-41ED-B882-1FA912257613}"/>
+    <hyperlink ref="A36" r:id="rId35" xr:uid="{BF2773B9-0B9D-43C3-95E8-34440AE113AB}"/>
+    <hyperlink ref="A37" r:id="rId36" xr:uid="{96FB93D6-A038-4BCF-8CCB-160DC1427C7B}"/>
+    <hyperlink ref="A38" r:id="rId37" xr:uid="{2BE13A4D-4EDE-48D5-9968-E48C1A9B1F93}"/>
+    <hyperlink ref="A39" r:id="rId38" xr:uid="{4C30EE42-3E4D-43F6-947F-4DAE206CA16A}"/>
+    <hyperlink ref="A40" r:id="rId39" xr:uid="{4C1DE4A6-FA96-47D8-B37F-77325F3C8585}"/>
+    <hyperlink ref="A41" r:id="rId40" xr:uid="{EB7C98AA-7A60-427A-ABB3-D38242719DD9}"/>
+    <hyperlink ref="A42" r:id="rId41" xr:uid="{C9AE9624-F8E3-43E3-96BA-0C381D0134E9}"/>
+    <hyperlink ref="A43" r:id="rId42" xr:uid="{C10996FC-F5D7-48C3-A9B3-FB6DE2AC421C}"/>
+    <hyperlink ref="A44" r:id="rId43" xr:uid="{A9EF09A4-ABA9-47DF-9B54-9BD9B8C49534}"/>
+    <hyperlink ref="A45" r:id="rId44" xr:uid="{7F1A1AD0-78A1-493F-A5CA-891A1D53C8FF}"/>
+    <hyperlink ref="A46" r:id="rId45" xr:uid="{C244A69C-968E-47BC-9E2E-F116FF34160A}"/>
+    <hyperlink ref="A47" r:id="rId46" xr:uid="{159D2D64-AC6F-4BF8-BEC3-F837F16DF4D6}"/>
+    <hyperlink ref="A48" r:id="rId47" xr:uid="{EDBA620F-4CC4-44EC-BCA4-B17CA30A2817}"/>
+    <hyperlink ref="A49" r:id="rId48" xr:uid="{783EE0C8-F706-4315-B30A-6CDF5679378F}"/>
+    <hyperlink ref="A50" r:id="rId49" xr:uid="{EA35BC55-72AB-4566-94E4-E32508FA3544}"/>
+    <hyperlink ref="A51" r:id="rId50" xr:uid="{3641BE2E-85A8-4842-8768-BB8118754ACD}"/>
+    <hyperlink ref="A52" r:id="rId51" xr:uid="{29B113A5-654A-43AC-8FEA-5A2C5297D1D7}"/>
+    <hyperlink ref="A53" r:id="rId52" xr:uid="{B833EFE4-4271-4787-A25C-7C5976257EEE}"/>
+    <hyperlink ref="A54" r:id="rId53" xr:uid="{AFBFB780-DD14-460F-941E-9E0226B75C76}"/>
+    <hyperlink ref="A55" r:id="rId54" xr:uid="{45241C60-49BD-4C1D-8526-1E133776C907}"/>
+    <hyperlink ref="A56" r:id="rId55" xr:uid="{B7324FB8-6FE1-4226-BB65-49A346A22B89}"/>
+    <hyperlink ref="A57" r:id="rId56" xr:uid="{8B0AF956-DD94-4EA4-8434-7C8FF9A56D72}"/>
+    <hyperlink ref="A58" r:id="rId57" xr:uid="{AFF4266F-4278-45A3-A5E9-23A327DD85D5}"/>
+    <hyperlink ref="A59" r:id="rId58" xr:uid="{52E06F97-E33B-4345-AA6A-754D87598FFD}"/>
+    <hyperlink ref="A60" r:id="rId59" xr:uid="{2382F8ED-A3E9-4365-8D9E-505C24481B43}"/>
+    <hyperlink ref="A61" r:id="rId60" xr:uid="{29C2DD67-B3A9-48A6-B3F3-5634D457FA0C}"/>
+    <hyperlink ref="A62" r:id="rId61" xr:uid="{FD07608F-BBBE-4730-A28A-73C0F4FC3C62}"/>
+    <hyperlink ref="A63" r:id="rId62" xr:uid="{E309C8D8-DB0B-4A6A-A508-C1314E211B91}"/>
+    <hyperlink ref="A64" r:id="rId63" xr:uid="{80D661F9-7BA9-49FA-A62E-DEF847ED0B0F}"/>
+    <hyperlink ref="A65" r:id="rId64" xr:uid="{4FA8B658-283F-48FD-98E5-B44A7DF255ED}"/>
+    <hyperlink ref="A66" r:id="rId65" xr:uid="{717D3D8C-A873-4B47-B53C-E3A6BF751880}"/>
+    <hyperlink ref="A67" r:id="rId66" xr:uid="{C6E74428-2EC2-4BB5-B488-BAB328873723}"/>
+    <hyperlink ref="A68" r:id="rId67" xr:uid="{7C2B27F5-E3BB-4B3B-9D39-4A32CFDBD302}"/>
+    <hyperlink ref="A69" r:id="rId68" xr:uid="{14094AC1-F36D-4578-8B48-F7CD18E09497}"/>
+    <hyperlink ref="A70" r:id="rId69" xr:uid="{802E7644-C3DC-48B0-81D1-62B58F33D664}"/>
+    <hyperlink ref="A71" r:id="rId70" xr:uid="{37F30E11-EBEB-4A36-983C-0820E68089F3}"/>
+    <hyperlink ref="A72" r:id="rId71" xr:uid="{919312C9-F809-4104-9355-209FFD2C100B}"/>
+    <hyperlink ref="A73" r:id="rId72" xr:uid="{0DB21D0F-E89F-469B-A5D4-F89650F33307}"/>
+    <hyperlink ref="A74" r:id="rId73" xr:uid="{E706336A-3E8B-4748-BF04-EC10D73E9FCC}"/>
+    <hyperlink ref="A75" r:id="rId74" xr:uid="{04A4C083-08A6-4C54-B898-8E2334B908CE}"/>
+    <hyperlink ref="A76" r:id="rId75" xr:uid="{F8CAD71C-01F4-44B8-B48C-89BDDF58DB77}"/>
+    <hyperlink ref="A77" r:id="rId76" xr:uid="{506A08B8-CAC3-467D-8CF2-8D1E25E58549}"/>
+    <hyperlink ref="A78" r:id="rId77" xr:uid="{ED7C9EC5-7B0D-4E26-8C47-FDC54B4C9FAA}"/>
+    <hyperlink ref="A79" r:id="rId78" xr:uid="{136EFF80-0156-4E06-AABC-A70A32A05351}"/>
+    <hyperlink ref="A80" r:id="rId79" xr:uid="{DF71940C-A911-4402-93FE-E48A3ED5FB12}"/>
+    <hyperlink ref="A81" r:id="rId80" xr:uid="{DC592959-D5BF-474A-A664-75B403FF3598}"/>
+    <hyperlink ref="A82" r:id="rId81" xr:uid="{DE88A214-6C25-49D5-8575-644C3F80A719}"/>
+    <hyperlink ref="A83" r:id="rId82" xr:uid="{ADC2C3ED-00C4-449F-B243-5E2D3E1F8443}"/>
+    <hyperlink ref="A84" r:id="rId83" xr:uid="{95DFE4D6-02F0-455A-A45B-ACADC2CFDECE}"/>
+    <hyperlink ref="A85" r:id="rId84" xr:uid="{E74B3376-4A17-423D-A9D2-F76A6E02F2F4}"/>
+    <hyperlink ref="A86" r:id="rId85" xr:uid="{FD832632-168D-440C-9502-BBA71C231B5C}"/>
+    <hyperlink ref="A87" r:id="rId86" xr:uid="{F6E1062C-8CB7-4268-9B47-753529F592DD}"/>
+    <hyperlink ref="A88" r:id="rId87" xr:uid="{E7C52048-9BE2-42DE-A766-5B421DF85704}"/>
+    <hyperlink ref="A89" r:id="rId88" xr:uid="{7B90C312-B515-466A-AED7-ABBBC33672B0}"/>
+    <hyperlink ref="A90" r:id="rId89" xr:uid="{F6135D2C-B634-4212-8C52-4F479406A4C7}"/>
+    <hyperlink ref="A91" r:id="rId90" xr:uid="{18195A65-5C29-42BC-B8ED-4D17B73D7E21}"/>
+    <hyperlink ref="A92" r:id="rId91" xr:uid="{9EBFD1F1-1426-4F13-9660-C3BBB1136639}"/>
+    <hyperlink ref="A93" r:id="rId92" xr:uid="{D875FE66-709F-4CE5-92CA-90745CC82F44}"/>
+    <hyperlink ref="A94" r:id="rId93" xr:uid="{E3622FC4-1998-4D6B-B834-53A02D6D9137}"/>
+    <hyperlink ref="A95" r:id="rId94" xr:uid="{18CC0249-86D1-4444-A5A9-F369A093965F}"/>
+    <hyperlink ref="A96" r:id="rId95" xr:uid="{6D8A3E9A-4174-4402-AE18-90F5FB650BEB}"/>
+    <hyperlink ref="A97" r:id="rId96" xr:uid="{D9C1DA77-4B6F-41F0-9BB2-63D286371EB1}"/>
+    <hyperlink ref="A98" r:id="rId97" xr:uid="{1B871517-9E32-4137-8E13-5C666F7F436B}"/>
+    <hyperlink ref="A99" r:id="rId98" xr:uid="{BC7C9C50-0F00-44B1-BC28-361199B0E6DC}"/>
+    <hyperlink ref="A100" r:id="rId99" xr:uid="{12B8BD6C-62B6-4A63-B06C-1383362A0B6F}"/>
+    <hyperlink ref="A101" r:id="rId100" xr:uid="{0532B51F-EFEE-40D0-8CD3-8635ED52F8B7}"/>
+    <hyperlink ref="A102" r:id="rId101" xr:uid="{F4EAA727-DFF6-4A94-ABD2-647B548C10AF}"/>
+    <hyperlink ref="A103" r:id="rId102" xr:uid="{1FEB28EE-7EBB-48C7-A9D6-98BB1F20B12A}"/>
+    <hyperlink ref="A104" r:id="rId103" xr:uid="{27240B6D-0A78-4E82-B3DA-A3132D140CE9}"/>
+    <hyperlink ref="A105" r:id="rId104" xr:uid="{33CD1905-EA0E-4D27-913A-ED918E501476}"/>
+    <hyperlink ref="A106" r:id="rId105" xr:uid="{BF51932A-3ADB-4BE5-AC47-2331089D25D4}"/>
+    <hyperlink ref="A107" r:id="rId106" xr:uid="{ED9C5948-E816-450B-A313-A4B0A5F5E302}"/>
+    <hyperlink ref="A108" r:id="rId107" xr:uid="{27DD160E-5049-44EE-A9D9-0CCA3448DDB3}"/>
+    <hyperlink ref="A109" r:id="rId108" xr:uid="{CB55DF4A-384D-4327-9BFF-268042EB2AC4}"/>
+    <hyperlink ref="A110" r:id="rId109" xr:uid="{72A8C03F-EE30-4254-947C-48F37A7A1C53}"/>
+    <hyperlink ref="A111" r:id="rId110" xr:uid="{502BCF1D-0406-4F1D-BC99-EF6B864F02AB}"/>
+    <hyperlink ref="A112" r:id="rId111" xr:uid="{AE2C28FC-AED2-4F78-8253-420EB89EF9F9}"/>
+    <hyperlink ref="A113" r:id="rId112" xr:uid="{6F89B95D-2F6D-4DE5-8D2F-C04F504EBE1D}"/>
+    <hyperlink ref="A114" r:id="rId113" xr:uid="{C9497621-2947-4F0C-9B8C-B3F5D5E1C5BE}"/>
+    <hyperlink ref="A115" r:id="rId114" xr:uid="{66C07805-8968-4D71-8690-780B007FB37F}"/>
+    <hyperlink ref="A116" r:id="rId115" xr:uid="{EA03FE43-D190-4FE4-81AF-C39CD527EDC0}"/>
+    <hyperlink ref="A117" r:id="rId116" xr:uid="{AA0D3FC3-A22B-4730-B712-3E35E4283277}"/>
+    <hyperlink ref="A118" r:id="rId117" xr:uid="{C955DB62-AD98-4753-9F47-E2DA454C555B}"/>
+    <hyperlink ref="A119" r:id="rId118" xr:uid="{6D74C340-96D6-4FDA-8310-F6CDED066B09}"/>
+    <hyperlink ref="A120" r:id="rId119" xr:uid="{2543CAF5-7820-4620-A6DF-9C7BCC5E9AA1}"/>
+    <hyperlink ref="A121" r:id="rId120" xr:uid="{6A25F517-130F-43B6-ACAE-3206FB67C16D}"/>
+    <hyperlink ref="A122" r:id="rId121" xr:uid="{CD278193-9F78-4A14-B99C-F58A468B0233}"/>
+    <hyperlink ref="A123" r:id="rId122" xr:uid="{ECCD16B6-73D5-44A3-B9E4-D7365F0DCCE7}"/>
+    <hyperlink ref="A124" r:id="rId123" xr:uid="{946DF065-CA65-4C48-812B-6E9B289EFA60}"/>
+    <hyperlink ref="A125" r:id="rId124" xr:uid="{FBCE05EF-9F0E-4F79-A420-80EB4E4BC021}"/>
+    <hyperlink ref="A126" r:id="rId125" xr:uid="{AAA8E962-1925-4B01-973D-DCBD5719FA69}"/>
+    <hyperlink ref="A127" r:id="rId126" xr:uid="{EDE4724A-5B84-47DA-8C2E-6A40DC0E0611}"/>
+    <hyperlink ref="A128" r:id="rId127" xr:uid="{626D1420-34F5-4A90-961D-D646D4760DB3}"/>
+    <hyperlink ref="A129" r:id="rId128" xr:uid="{26D81A55-AF4B-4746-B0B5-0F4CAD349A42}"/>
+    <hyperlink ref="A130" r:id="rId129" xr:uid="{4A07C653-AE3A-4CBC-A27B-A2984C7CFB20}"/>
+    <hyperlink ref="A131" r:id="rId130" xr:uid="{AA63E2F9-0E3D-41D7-85BD-693168450EF2}"/>
+    <hyperlink ref="A132" r:id="rId131" xr:uid="{1A64DF57-F7DA-4C4E-A058-275882888771}"/>
+    <hyperlink ref="A133" r:id="rId132" xr:uid="{BA4061D5-A12C-4C6E-8A31-E52B732EE99B}"/>
+    <hyperlink ref="A134" r:id="rId133" xr:uid="{6B30C0BE-B917-44F7-AAEC-87076E780311}"/>
+    <hyperlink ref="A135" r:id="rId134" xr:uid="{26EF3D80-178E-48D6-AA2D-EC0582B307AD}"/>
+    <hyperlink ref="A136" r:id="rId135" xr:uid="{5FE8591D-F846-49C0-9759-E34871EA3FD8}"/>
+    <hyperlink ref="A137" r:id="rId136" xr:uid="{4A5D6DE8-3513-404F-98B7-BE8FFC46065A}"/>
+    <hyperlink ref="A138" r:id="rId137" xr:uid="{A3AF704A-0EAC-4214-AB5F-01F865686ED2}"/>
+    <hyperlink ref="A139" r:id="rId138" xr:uid="{3B32A6D0-E7E8-4A54-A7B0-64595BF7BB45}"/>
+    <hyperlink ref="A140" r:id="rId139" xr:uid="{AC1BC55C-EEA8-4F73-920C-968A8C7C059C}"/>
+    <hyperlink ref="A141" r:id="rId140" xr:uid="{5C802731-203A-4DE7-8EE7-0673A9152485}"/>
+    <hyperlink ref="A142" r:id="rId141" xr:uid="{E46FEB0F-D1A5-466F-9038-A87414622BEB}"/>
+    <hyperlink ref="A143" r:id="rId142" xr:uid="{86C122A7-3023-4479-9839-C83A80133DAB}"/>
+    <hyperlink ref="A144" r:id="rId143" xr:uid="{0F185557-6FB7-4538-83FF-3A197A28C2F9}"/>
+    <hyperlink ref="A145" r:id="rId144" xr:uid="{B264B94D-7C44-4102-88BA-5B6686DF45FC}"/>
+    <hyperlink ref="A146" r:id="rId145" xr:uid="{DF7B5583-F40E-4CA8-A0A3-63C213D7091C}"/>
+    <hyperlink ref="A147" r:id="rId146" xr:uid="{DE92D4E7-9F02-4694-9129-B8863538A5AA}"/>
+    <hyperlink ref="A148" r:id="rId147" xr:uid="{4468B4BB-E99F-4B86-B507-7F41B9016489}"/>
+    <hyperlink ref="A149" r:id="rId148" xr:uid="{754121B0-F226-4A86-BFAF-CEF72989B2A0}"/>
+    <hyperlink ref="A150" r:id="rId149" xr:uid="{7B5AA3C9-065B-43E3-9EB4-488EFDD3AE6F}"/>
+    <hyperlink ref="A151" r:id="rId150" xr:uid="{E328743A-362E-430B-A923-95F5DC62CBD4}"/>
+    <hyperlink ref="A152" r:id="rId151" xr:uid="{39246FBA-F6CC-48D7-8DE5-AB1B857FA949}"/>
+    <hyperlink ref="A153" r:id="rId152" xr:uid="{8647A75B-8E59-4EE3-B5E6-B448C3CD4A41}"/>
+    <hyperlink ref="A154" r:id="rId153" xr:uid="{3BFD4A55-9951-4E18-BB53-AA8E0DF4114D}"/>
+    <hyperlink ref="A155" r:id="rId154" xr:uid="{4891CB6F-2B43-4CE8-ABA0-3FFC379ACDA2}"/>
+    <hyperlink ref="A156" r:id="rId155" xr:uid="{3D017249-249E-4117-AF16-7CB37AB9D9F1}"/>
+    <hyperlink ref="A157" r:id="rId156" xr:uid="{05CEF3E4-79EF-4215-895D-D3846242E4CC}"/>
+    <hyperlink ref="A158" r:id="rId157" xr:uid="{6B7310AF-645C-40C5-BBBD-7772E273B0B6}"/>
+    <hyperlink ref="A159" r:id="rId158" xr:uid="{FA6EE7EE-305A-4DA7-A96E-B16DDBAC66F4}"/>
+    <hyperlink ref="A160" r:id="rId159" xr:uid="{B4F032AA-EA64-4872-8A86-0BC10AFAB5CB}"/>
+    <hyperlink ref="A161" r:id="rId160" xr:uid="{9FA5813D-2A16-42C2-8164-4334AB74F22B}"/>
+    <hyperlink ref="A162" r:id="rId161" xr:uid="{F40280E9-53AA-4BE7-AC64-2BF2D8650B78}"/>
+    <hyperlink ref="A163" r:id="rId162" xr:uid="{3D0C1FD8-FC9E-49F8-B07A-98CF62A46E74}"/>
+    <hyperlink ref="A164" r:id="rId163" xr:uid="{999BA9DA-6DA6-4A98-9DAD-081DFD6C8A76}"/>
+    <hyperlink ref="A165" r:id="rId164" xr:uid="{13D5B3D7-980B-4742-BBB5-62035C31D6BA}"/>
+    <hyperlink ref="A166" r:id="rId165" xr:uid="{7AE30300-1BFF-4FEF-BCBB-A89DC97C9AFD}"/>
+    <hyperlink ref="A167" r:id="rId166" xr:uid="{680A205F-1943-4892-B74A-3C28617FD230}"/>
+    <hyperlink ref="A168" r:id="rId167" xr:uid="{0738E3D4-3165-483C-AD41-B31F4B7FB1D8}"/>
+    <hyperlink ref="A169" r:id="rId168" xr:uid="{4754A22B-B899-45B0-88A2-86CCC49A3D07}"/>
+    <hyperlink ref="A170" r:id="rId169" xr:uid="{C0021682-4B61-4E14-A2F5-8B605F0045AA}"/>
+    <hyperlink ref="A171" r:id="rId170" xr:uid="{5BBB4278-43A1-44B1-A425-E1FF6DD7D669}"/>
+    <hyperlink ref="A172" r:id="rId171" xr:uid="{40F18247-D143-49D5-B7F6-8A4F2CD1F238}"/>
+    <hyperlink ref="A173" r:id="rId172" xr:uid="{EA8126C5-3569-457F-AF2A-516A3EF08EC2}"/>
+    <hyperlink ref="A174" r:id="rId173" xr:uid="{750E7A47-2599-4315-92BE-7AA4E6CB1690}"/>
+    <hyperlink ref="A175" r:id="rId174" xr:uid="{A32690AD-DB69-4572-982D-03979340A3C1}"/>
+    <hyperlink ref="A176" r:id="rId175" xr:uid="{C3C7FB93-AE2D-444B-B69A-09BA56705223}"/>
+    <hyperlink ref="A177" r:id="rId176" xr:uid="{BF369D16-1A9E-4BFC-80DC-5211E3E0905A}"/>
+    <hyperlink ref="A178" r:id="rId177" xr:uid="{A6EA0F8F-24B1-4863-BF00-289942F31B54}"/>
+    <hyperlink ref="A179" r:id="rId178" xr:uid="{ABD2E4B6-5A79-4E6E-B313-7D0946DE7B5D}"/>
+    <hyperlink ref="A180" r:id="rId179" xr:uid="{551ADC55-B629-45D5-89ED-075B37079FAB}"/>
+    <hyperlink ref="A181" r:id="rId180" xr:uid="{C13F0D9E-2C3E-448F-8D52-1576969D4E6D}"/>
+    <hyperlink ref="A182" r:id="rId181" xr:uid="{780B5353-BDB2-4E1B-8C80-56FD047BCF77}"/>
+    <hyperlink ref="A183" r:id="rId182" xr:uid="{A65E4975-A1FC-40BA-89EA-7287E4B60D36}"/>
+    <hyperlink ref="A184" r:id="rId183" xr:uid="{6295BC3B-E49F-4A9B-BC84-BBBA91084433}"/>
+    <hyperlink ref="A185" r:id="rId184" xr:uid="{D4BFF236-8DE5-42B1-865E-1A353921577C}"/>
+    <hyperlink ref="A186" r:id="rId185" xr:uid="{BE220AD5-26E7-44E0-BEDA-CE00D96076D0}"/>
+    <hyperlink ref="A187" r:id="rId186" xr:uid="{D377A7AD-73E3-4530-932E-0E73BEFAE32B}"/>
+    <hyperlink ref="A188" r:id="rId187" xr:uid="{9186A970-A69F-4EA9-8277-DA669327CA32}"/>
+    <hyperlink ref="A189" r:id="rId188" xr:uid="{A97BB54E-C501-4571-A388-39E6A5A33BE1}"/>
+    <hyperlink ref="A190" r:id="rId189" xr:uid="{1B8E6228-2B0C-4712-A152-179E32850572}"/>
+    <hyperlink ref="A191" r:id="rId190" xr:uid="{CC81BD2E-A6C2-45E4-88A6-C504D3CFEB67}"/>
+    <hyperlink ref="A192" r:id="rId191" xr:uid="{4B66351D-EB53-47E5-8A54-6E0FF7AB48AC}"/>
+    <hyperlink ref="A193" r:id="rId192" xr:uid="{FB9ABC87-2BA0-4E94-9B60-24F16E3A5BD4}"/>
+    <hyperlink ref="A194" r:id="rId193" xr:uid="{231D640E-133B-4709-9C32-D449EFFFD51C}"/>
+    <hyperlink ref="A195" r:id="rId194" xr:uid="{90AE84CE-58EE-49F3-A294-CEEFE3461D92}"/>
+    <hyperlink ref="A196" r:id="rId195" xr:uid="{A015A4DF-895B-43B1-A74A-242847EBF0D3}"/>
+    <hyperlink ref="A197" r:id="rId196" xr:uid="{08783F74-B818-4127-AE45-D33D1D5BE6EA}"/>
+    <hyperlink ref="A198" r:id="rId197" xr:uid="{2596E95F-441B-4058-858A-931E81AC9E1C}"/>
+    <hyperlink ref="A199" r:id="rId198" xr:uid="{7B40B1F5-8354-4075-8386-35156578397F}"/>
+    <hyperlink ref="A200" r:id="rId199" xr:uid="{4C765F17-6D19-4E32-9694-5977D3A22723}"/>
+    <hyperlink ref="A201" r:id="rId200" xr:uid="{1C968D84-7BDB-4082-9BAF-9FD098570EA3}"/>
+    <hyperlink ref="A202" r:id="rId201" xr:uid="{8C71850A-1573-4AE2-AA37-FFD2131097A8}"/>
+    <hyperlink ref="A203" r:id="rId202" xr:uid="{9EAEF1B5-2818-4A01-945C-EE151B6DD741}"/>
+    <hyperlink ref="A204" r:id="rId203" xr:uid="{545BB44B-5C81-4FA2-98BE-BF7206EC6955}"/>
+    <hyperlink ref="A205" r:id="rId204" xr:uid="{63E22789-0BA3-45B7-91BB-EF79A041357F}"/>
+    <hyperlink ref="A206" r:id="rId205" xr:uid="{98ABB564-05B3-40CE-8D8B-7960D3DEFACF}"/>
+    <hyperlink ref="A207" r:id="rId206" xr:uid="{FFF04351-85E1-4715-B2FE-0BF696F22BFE}"/>
+    <hyperlink ref="A208" r:id="rId207" xr:uid="{B4B48D38-83F2-4791-BAE8-D2F96A1C1F9B}"/>
+    <hyperlink ref="A209" r:id="rId208" xr:uid="{D8562727-DA6F-4A3F-813D-869105DE1D88}"/>
+    <hyperlink ref="A210" r:id="rId209" xr:uid="{5E971897-5C81-4531-A5B2-20980E79D087}"/>
+    <hyperlink ref="A211" r:id="rId210" xr:uid="{30EF7F30-D3BC-4A18-9818-83283A54A69E}"/>
+    <hyperlink ref="A212" r:id="rId211" xr:uid="{CC0DF168-CF83-4B6C-BABC-4AF27B125521}"/>
+    <hyperlink ref="A213" r:id="rId212" xr:uid="{B4C7D1C8-C44F-4B7A-90A1-180AB66DD5D9}"/>
+    <hyperlink ref="A214" r:id="rId213" xr:uid="{24DB8D6F-10A7-442E-822C-754CC5F31AEF}"/>
+    <hyperlink ref="A215" r:id="rId214" xr:uid="{31CB3A5C-B4C9-4F49-AAA1-A12218AA0995}"/>
+    <hyperlink ref="A216" r:id="rId215" xr:uid="{29B3DA1C-E7C0-4600-B397-7E5A92D7335F}"/>
+    <hyperlink ref="A217" r:id="rId216" xr:uid="{EC4C5B92-C108-4774-8F4B-BD050AEF8EEA}"/>
+    <hyperlink ref="A218" r:id="rId217" xr:uid="{B3EEF0ED-EC93-490B-B05D-20CA992662EC}"/>
+    <hyperlink ref="A219" r:id="rId218" xr:uid="{98AFA4C5-8A04-4012-A04E-A233CFDD7D1C}"/>
+    <hyperlink ref="A220" r:id="rId219" xr:uid="{6D85FD9A-5F58-499F-87E4-6CAD880165B7}"/>
+    <hyperlink ref="A221" r:id="rId220" xr:uid="{30DE2FEC-B4F5-45C5-A2ED-ABF73DC4DBD6}"/>
+    <hyperlink ref="A222" r:id="rId221" xr:uid="{0CDA986F-7730-4466-9EA6-20575837AC24}"/>
+    <hyperlink ref="A223" r:id="rId222" xr:uid="{DF35FC23-DCD1-46B6-82DE-7CF00C2BA89B}"/>
+    <hyperlink ref="A224" r:id="rId223" xr:uid="{3196584D-66A0-43C5-9647-5117F9082362}"/>
+    <hyperlink ref="A225" r:id="rId224" xr:uid="{7DFD2850-8F75-471B-918B-D855693972CA}"/>
+    <hyperlink ref="A226" r:id="rId225" xr:uid="{E8CEF776-37B9-4C2F-A257-B94F17AD0ECA}"/>
+    <hyperlink ref="A227" r:id="rId226" xr:uid="{BBF43CFD-9DCF-44D8-AD5B-C88C2237A58A}"/>
+    <hyperlink ref="A228" r:id="rId227" xr:uid="{FF334303-5C0A-4986-8CC2-500E202AE518}"/>
+    <hyperlink ref="A229" r:id="rId228" xr:uid="{A58EF837-A1F3-4DD2-97AC-1E61D06E9F15}"/>
+    <hyperlink ref="A230" r:id="rId229" xr:uid="{DCB4538A-89CB-4D70-8471-7B9D5FD5EAB7}"/>
+    <hyperlink ref="A231" r:id="rId230" xr:uid="{82E33D1C-0493-4ACB-B613-FE5A1A69F2B3}"/>
+    <hyperlink ref="A232" r:id="rId231" xr:uid="{45F610C4-347E-4EC6-82DA-802DFC05DB50}"/>
+    <hyperlink ref="A233" r:id="rId232" xr:uid="{F2BDE735-E544-48FF-BEBF-F44520901F1A}"/>
+    <hyperlink ref="A234" r:id="rId233" xr:uid="{ECABD109-7589-4610-B0C8-25B8103E3697}"/>
+    <hyperlink ref="A235" r:id="rId234" xr:uid="{A27EDF37-085B-45E6-92B8-16FA715C0268}"/>
+    <hyperlink ref="A236" r:id="rId235" xr:uid="{660E5052-0820-40D8-88C3-BEDBFB1CACCF}"/>
+    <hyperlink ref="A237" r:id="rId236" xr:uid="{56AF5264-3510-4CAB-83A3-3335DAECE308}"/>
+    <hyperlink ref="A238" r:id="rId237" xr:uid="{B2C73A19-2550-47E8-AA9B-B7674AAB89F9}"/>
+    <hyperlink ref="A239" r:id="rId238" xr:uid="{86849C4D-EF56-4C5D-B256-6951CE5CC889}"/>
+    <hyperlink ref="A240" r:id="rId239" xr:uid="{D36D4641-A885-478B-A8C4-F1E206EC63D0}"/>
+    <hyperlink ref="A241" r:id="rId240" xr:uid="{19FB4A44-FF04-43EE-98D1-9E73E79148C9}"/>
+    <hyperlink ref="A242" r:id="rId241" xr:uid="{2AE93FF2-10C5-4B6A-BE4C-2B5A96DDFB18}"/>
+    <hyperlink ref="A243" r:id="rId242" xr:uid="{2D7FEF9C-8E52-4908-B786-75553032DE38}"/>
+    <hyperlink ref="A244" r:id="rId243" xr:uid="{49D98DCD-BDCA-4658-BC2B-D3F673E526D6}"/>
+    <hyperlink ref="A245" r:id="rId244" xr:uid="{5187A460-9718-4E9B-A822-F2710ACBAA2A}"/>
+    <hyperlink ref="A246" r:id="rId245" xr:uid="{A87DD550-5782-4EEC-B238-CDDEB891DF6B}"/>
+    <hyperlink ref="A247" r:id="rId246" xr:uid="{B3FA13A2-8E98-4CE6-BFD6-E3B6B3454883}"/>
+    <hyperlink ref="A248" r:id="rId247" xr:uid="{ED124DC6-AE60-4DE3-988B-AB09BDB830BA}"/>
+    <hyperlink ref="A249" r:id="rId248" xr:uid="{81D0DD2E-FE52-4778-BD78-12A873338C50}"/>
+    <hyperlink ref="A250" r:id="rId249" xr:uid="{D5F68589-D79F-42F1-896B-D93FAD39CEF9}"/>
+    <hyperlink ref="A251" r:id="rId250" xr:uid="{FF1CD754-D11D-40C2-BA29-2F49B4703629}"/>
+    <hyperlink ref="A252" r:id="rId251" xr:uid="{61A568D6-C475-453E-BB2E-27515DE7DC53}"/>
+    <hyperlink ref="A253" r:id="rId252" xr:uid="{3A5D991B-246F-4786-9179-2169097084B6}"/>
+    <hyperlink ref="A254" r:id="rId253" xr:uid="{28CA2C99-9D2E-424A-B136-3C10D3B00623}"/>
+    <hyperlink ref="A255" r:id="rId254" xr:uid="{2BA6CF2F-72E3-4556-8B45-FC912A616B31}"/>
+    <hyperlink ref="A256" r:id="rId255" xr:uid="{B8BD4C12-91DE-4E21-856C-828CA7D5956F}"/>
+    <hyperlink ref="A257" r:id="rId256" xr:uid="{1F7C288D-705A-4A32-88AA-7D156E657307}"/>
+    <hyperlink ref="A258" r:id="rId257" xr:uid="{30D56278-A4F5-4C8E-A33A-86B94EC60A71}"/>
+    <hyperlink ref="A259" r:id="rId258" xr:uid="{51BC8451-D8DD-48D4-8748-8EEB49CCE40D}"/>
+    <hyperlink ref="A260" r:id="rId259" xr:uid="{B45BDD6A-507E-4FEF-9AAC-91F90EA89FC1}"/>
+    <hyperlink ref="A261" r:id="rId260" xr:uid="{EC9D5AA4-A2E4-4E20-BFB6-722E648C499F}"/>
+    <hyperlink ref="A262" r:id="rId261" xr:uid="{2DE98CA5-135E-475F-B08E-977CFF6B5C76}"/>
+    <hyperlink ref="A263" r:id="rId262" xr:uid="{8E4F4EC5-E2E7-4ABB-9173-B1F8B8D46765}"/>
+    <hyperlink ref="A264" r:id="rId263" xr:uid="{ED2D02A2-8413-4386-837C-2E242899D90D}"/>
+    <hyperlink ref="A265" r:id="rId264" xr:uid="{3471C7C8-1088-4127-AB05-819546219BAB}"/>
+    <hyperlink ref="A266" r:id="rId265" xr:uid="{979587BD-E48C-43DC-B083-D582400DEE92}"/>
+    <hyperlink ref="A267" r:id="rId266" xr:uid="{0A16951B-4330-4A02-9BF9-892EB57388C0}"/>
+    <hyperlink ref="A268" r:id="rId267" xr:uid="{31898C26-72E7-4EEE-B437-42C5E2F4F1D6}"/>
+    <hyperlink ref="A269" r:id="rId268" xr:uid="{5C73DDFC-2E2B-49A1-BD54-D5B01BAF4AF1}"/>
+    <hyperlink ref="A270" r:id="rId269" xr:uid="{31FF6CBD-7AB8-48DD-ABEA-B3E40F4DC8A0}"/>
+    <hyperlink ref="A271" r:id="rId270" xr:uid="{1F6DA59C-2C98-496D-BC04-23F90FFEFA88}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId261"/>
+    <tablePart r:id="rId271"/>
   </tableParts>
 </worksheet>
 </file>